--- a/results/RQ2/analysis_results_raw.xlsx
+++ b/results/RQ2/analysis_results_raw.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,81 +413,96 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O65"/>
+  <dimension ref="A1:R65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Prática</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Atributo</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Likert Média</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Média direto</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Média indireto</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Practice</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Attribute</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Overall Mean</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Mean Direct</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Mean Indirect</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
         <is>
           <t>P-value Direct/Indirect</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>P-value Holm Direct/Indirect</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
         <is>
           <t>Effect Size Direct/Indirect</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Média Grande</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Média Pequena</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Mean Large</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Mean Small</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
         <is>
           <t>P-value Big/Small</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>P-value Holm Big/Small</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
         <is>
           <t>Effect Size Big/Small</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>Média Especialista</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>Média Não-Especialista</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Mean Specialist</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Mean Non-Specialist</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
         <is>
           <t>P-value Specialist/Non-Specialist</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>P-value Holm Specialist/Non-Specialist</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
         <is>
           <t>Effect Size Specialist/Non-Specialist</t>
         </is>
@@ -508,16 +511,16 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Revisão de Código</t>
+          <t>Code Review</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>facilidade</t>
+          <t>Ease of use</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>3.084337349397591</v>
+        <v>3.555555555555555</v>
       </c>
       <c r="D2" t="n">
         <v>3.596491228070176</v>
@@ -526,55 +529,64 @@
         <v>3.4</v>
       </c>
       <c r="F2" t="n">
-        <v>0.3726463063168448</v>
-      </c>
-      <c r="G2" t="inlineStr">
+        <v>0.7452926126336895</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H2" t="inlineStr">
         <is>
           <t>(0.05380116959064327, 'negligible')</t>
         </is>
       </c>
-      <c r="H2" t="n">
+      <c r="I2" t="n">
         <v>3.618181818181818</v>
       </c>
-      <c r="I2" t="n">
+      <c r="J2" t="n">
         <v>3.533333333333333</v>
       </c>
-      <c r="J2" t="n">
-        <v>0.3350249944387612</v>
-      </c>
-      <c r="K2" t="inlineStr">
+      <c r="K2" t="n">
+        <v>0.6700499888775223</v>
+      </c>
+      <c r="L2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M2" t="inlineStr">
         <is>
           <t>(0.0703030303030303, 'negligible')</t>
         </is>
       </c>
-      <c r="L2" t="n">
-        <v>3.090909090909091</v>
-      </c>
-      <c r="M2" t="n">
-        <v>3.76</v>
-      </c>
       <c r="N2" t="n">
-        <v>0.9920700764609476</v>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>(-0.34363636363636363, 'medium')</t>
+        <v>3.5</v>
+      </c>
+      <c r="O2" t="n">
+        <v>3.666666666666667</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0.521800834942814</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>1</v>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>(-0.09027777777777778, 'negligible')</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Modelagem de Ameaças</t>
+          <t>Threat Modeling</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>facilidade</t>
+          <t>Ease of use</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2.457831325301205</v>
+        <v>3.238095238095238</v>
       </c>
       <c r="D3" t="n">
         <v>3.283018867924528</v>
@@ -583,55 +595,64 @@
         <v>3</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1806241396079169</v>
-      </c>
-      <c r="G3" t="inlineStr">
+        <v>0.3612482792158338</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H3" t="inlineStr">
         <is>
           <t>(0.17735849056603772, 'small')</t>
         </is>
       </c>
-      <c r="H3" t="n">
+      <c r="I3" t="n">
         <v>3.244897959183673</v>
       </c>
-      <c r="I3" t="n">
+      <c r="J3" t="n">
         <v>3.230769230769231</v>
       </c>
-      <c r="J3" t="n">
-        <v>0.3969205100110033</v>
-      </c>
-      <c r="K3" t="inlineStr">
+      <c r="K3" t="n">
+        <v>0.7938410200220065</v>
+      </c>
+      <c r="L3" t="n">
+        <v>1</v>
+      </c>
+      <c r="M3" t="inlineStr">
         <is>
           <t>(0.04709576138147567, 'negligible')</t>
         </is>
       </c>
-      <c r="L3" t="n">
-        <v>3.1875</v>
-      </c>
-      <c r="M3" t="n">
-        <v>3.25531914893617</v>
-      </c>
       <c r="N3" t="n">
-        <v>0.4704357995235507</v>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>(0.013297872340425532, 'negligible')</t>
+        <v>3.346938775510204</v>
+      </c>
+      <c r="O3" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0.07547516065860155</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>1</v>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>(0.30174927113702626, 'small')</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Identificação de Casos de Abuso/Mau Uso</t>
+          <t>Identifying Abuse/Misuse Cases</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>facilidade</t>
+          <t>Ease of use</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2.349397590361446</v>
+        <v>3</v>
       </c>
       <c r="D4" t="n">
         <v>3.111111111111111</v>
@@ -640,55 +661,64 @@
         <v>2.454545454545455</v>
       </c>
       <c r="F4" t="n">
-        <v>0.02065558980934877</v>
-      </c>
-      <c r="G4" t="inlineStr">
+        <v>0.04131117961869755</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.6609788738991608</v>
+      </c>
+      <c r="H4" t="inlineStr">
         <is>
           <t>(0.3602693602693603, 'medium')</t>
         </is>
       </c>
-      <c r="H4" t="n">
+      <c r="I4" t="n">
         <v>2.96</v>
       </c>
-      <c r="I4" t="n">
+      <c r="J4" t="n">
         <v>3.142857142857143</v>
       </c>
-      <c r="J4" t="n">
-        <v>0.705593313416951</v>
-      </c>
-      <c r="K4" t="inlineStr">
+      <c r="K4" t="n">
+        <v>0.6010903029180293</v>
+      </c>
+      <c r="L4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M4" t="inlineStr">
         <is>
           <t>(-0.08571428571428572, 'negligible')</t>
         </is>
       </c>
-      <c r="L4" t="n">
-        <v>2.888888888888889</v>
-      </c>
-      <c r="M4" t="n">
-        <v>3.042553191489362</v>
-      </c>
       <c r="N4" t="n">
-        <v>0.6906386548290177</v>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>(-0.07210401891252956, 'negligible')</t>
+        <v>3.142857142857143</v>
+      </c>
+      <c r="O4" t="n">
+        <v>2.5625</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0.03080522874317228</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0.4928836598907565</v>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>(0.33163265306122447, 'medium')</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Análise de Riscos Arquiteturais</t>
+          <t>Architectural Risk Analysis</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>facilidade</t>
+          <t>Ease of use</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2.493975903614458</v>
+        <v>3</v>
       </c>
       <c r="D5" t="n">
         <v>3.051724137931035</v>
@@ -697,55 +727,64 @@
         <v>2.727272727272727</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1984848858042937</v>
-      </c>
-      <c r="G5" t="inlineStr">
+        <v>0.3969697716085874</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H5" t="inlineStr">
         <is>
           <t>(0.15830721003134796, 'small')</t>
         </is>
       </c>
-      <c r="H5" t="n">
+      <c r="I5" t="n">
         <v>3.074074074074074</v>
       </c>
-      <c r="I5" t="n">
+      <c r="J5" t="n">
         <v>2.785714285714286</v>
       </c>
-      <c r="J5" t="n">
-        <v>0.1735315067680593</v>
-      </c>
-      <c r="K5" t="inlineStr">
+      <c r="K5" t="n">
+        <v>0.3470630135361186</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1</v>
+      </c>
+      <c r="M5" t="inlineStr">
         <is>
           <t>(0.16005291005291006, 'small')</t>
         </is>
       </c>
-      <c r="L5" t="n">
-        <v>2.863636363636364</v>
-      </c>
-      <c r="M5" t="n">
-        <v>3.063829787234043</v>
-      </c>
       <c r="N5" t="n">
-        <v>0.7231318065260695</v>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>(-0.0851063829787234, 'negligible')</t>
+        <v>3.115384615384615</v>
+      </c>
+      <c r="O5" t="n">
+        <v>2.647058823529412</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0.1235741928676162</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>1</v>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>(0.24321266968325791, 'small')</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Testes de Penetração</t>
+          <t>Penetration Testing</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>facilidade</t>
+          <t>Ease of use</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2.602409638554217</v>
+        <v>3.176470588235294</v>
       </c>
       <c r="D6" t="n">
         <v>3.189655172413793</v>
@@ -754,55 +793,64 @@
         <v>3.1</v>
       </c>
       <c r="F6" t="n">
-        <v>0.4574813087110049</v>
-      </c>
-      <c r="G6" t="inlineStr">
+        <v>0.9149626174220098</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" t="inlineStr">
         <is>
           <t>(0.022413793103448276, 'negligible')</t>
         </is>
       </c>
-      <c r="H6" t="n">
+      <c r="I6" t="n">
         <v>3.192307692307693</v>
       </c>
-      <c r="I6" t="n">
+      <c r="J6" t="n">
         <v>3.142857142857143</v>
       </c>
-      <c r="J6" t="n">
-        <v>0.4456015311617267</v>
-      </c>
-      <c r="K6" t="inlineStr">
+      <c r="K6" t="n">
+        <v>0.8912030623234534</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1</v>
+      </c>
+      <c r="M6" t="inlineStr">
         <is>
           <t>(0.024725274725274724, 'negligible')</t>
         </is>
       </c>
-      <c r="L6" t="n">
-        <v>3</v>
-      </c>
-      <c r="M6" t="n">
-        <v>3.266666666666667</v>
-      </c>
       <c r="N6" t="n">
-        <v>0.7879569772647925</v>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>(-0.11497584541062802, 'negligible')</t>
+        <v>3.245283018867925</v>
+      </c>
+      <c r="O6" t="n">
+        <v>2.933333333333333</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0.4292622096177933</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>1</v>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>(0.1320754716981132, 'negligible')</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Gerenciamento de Riscos</t>
+          <t>Risk Management</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>facilidade</t>
+          <t>Ease of use</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2.445783132530121</v>
+        <v>3.123076923076924</v>
       </c>
       <c r="D7" t="n">
         <v>3.166666666666667</v>
@@ -811,55 +859,64 @@
         <v>2.909090909090909</v>
       </c>
       <c r="F7" t="n">
-        <v>0.2956921913976033</v>
-      </c>
-      <c r="G7" t="inlineStr">
+        <v>0.5913843827952067</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" t="inlineStr">
         <is>
           <t>(0.09932659932659933, 'negligible')</t>
         </is>
       </c>
-      <c r="H7" t="n">
+      <c r="I7" t="n">
         <v>3.142857142857143</v>
       </c>
-      <c r="I7" t="n">
+      <c r="J7" t="n">
         <v>3.214285714285714</v>
       </c>
-      <c r="J7" t="n">
-        <v>0.5899747941498303</v>
-      </c>
-      <c r="K7" t="inlineStr">
+      <c r="K7" t="n">
+        <v>0.8336819822866175</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1</v>
+      </c>
+      <c r="M7" t="inlineStr">
         <is>
           <t>(-0.03644314868804665, 'negligible')</t>
         </is>
       </c>
-      <c r="L7" t="n">
-        <v>3.095238095238095</v>
-      </c>
-      <c r="M7" t="n">
-        <v>3.136363636363636</v>
-      </c>
       <c r="N7" t="n">
-        <v>0.4527417841877206</v>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>(0.0183982683982684, 'negligible')</t>
+        <v>3.1875</v>
+      </c>
+      <c r="O7" t="n">
+        <v>2.941176470588236</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0.3722043483469435</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1</v>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>(0.13970588235294118, 'negligible')</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Gerenciamento de Vulnerabilidades</t>
+          <t>Vulnerability Management</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>facilidade</t>
+          <t>Ease of use</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2.951807228915662</v>
+        <v>3.5</v>
       </c>
       <c r="D8" t="n">
         <v>3.482758620689655</v>
@@ -868,55 +925,64 @@
         <v>3.583333333333333</v>
       </c>
       <c r="F8" t="n">
-        <v>0.6104287967573402</v>
-      </c>
-      <c r="G8" t="inlineStr">
+        <v>0.7918257533349962</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" t="inlineStr">
         <is>
           <t>(-0.04741379310344827, 'negligible')</t>
         </is>
       </c>
-      <c r="H8" t="n">
+      <c r="I8" t="n">
         <v>3.509433962264151</v>
       </c>
-      <c r="I8" t="n">
+      <c r="J8" t="n">
         <v>3.533333333333333</v>
       </c>
-      <c r="J8" t="n">
-        <v>0.5155474577561279</v>
-      </c>
-      <c r="K8" t="inlineStr">
+      <c r="K8" t="n">
+        <v>0.9813400268213098</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1</v>
+      </c>
+      <c r="M8" t="inlineStr">
         <is>
           <t>(-0.005031446540880503, 'negligible')</t>
         </is>
       </c>
-      <c r="L8" t="n">
-        <v>3.363636363636364</v>
-      </c>
-      <c r="M8" t="n">
-        <v>3.5625</v>
-      </c>
       <c r="N8" t="n">
-        <v>0.7441613142972103</v>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>(-0.09185606060606061, 'negligible')</t>
+        <v>3.461538461538462</v>
+      </c>
+      <c r="O8" t="n">
+        <v>3.611111111111111</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0.6904087206464151</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1</v>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>(-0.060897435897435896, 'negligible')</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Testes de Segurança Manuais/Automatizados</t>
+          <t>Manual/Automated Security Testing</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>facilidade</t>
+          <t>Ease of use</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2.867469879518072</v>
+        <v>3.4</v>
       </c>
       <c r="D9" t="n">
         <v>3.379310344827586</v>
@@ -925,55 +991,64 @@
         <v>3.5</v>
       </c>
       <c r="F9" t="n">
-        <v>0.6445025770940875</v>
-      </c>
-      <c r="G9" t="inlineStr">
+        <v>0.7230310927504837</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" t="inlineStr">
         <is>
           <t>(-0.06465517241379311, 'negligible')</t>
         </is>
       </c>
-      <c r="H9" t="n">
+      <c r="I9" t="n">
         <v>3.518518518518519</v>
       </c>
-      <c r="I9" t="n">
+      <c r="J9" t="n">
         <v>3</v>
       </c>
-      <c r="J9" t="n">
-        <v>0.06631735808845449</v>
-      </c>
-      <c r="K9" t="inlineStr">
+      <c r="K9" t="n">
+        <v>0.132634716176909</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1</v>
+      </c>
+      <c r="M9" t="inlineStr">
         <is>
           <t>(0.2552910052910053, 'small')</t>
         </is>
       </c>
-      <c r="L9" t="n">
-        <v>3.416666666666667</v>
-      </c>
-      <c r="M9" t="n">
-        <v>3.391304347826087</v>
-      </c>
       <c r="N9" t="n">
-        <v>0.5102046229036937</v>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>(-0.002717391304347826, 'negligible')</t>
+        <v>3.403846153846154</v>
+      </c>
+      <c r="O9" t="n">
+        <v>3.388888888888889</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0.9225350974048464</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1</v>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>(0.016025641025641024, 'negligible')</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Execução de Testes Fuzz</t>
+          <t>Performing Fuzz Testing</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>facilidade</t>
+          <t>Ease of use</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>2.096385542168675</v>
+        <v>3.163636363636364</v>
       </c>
       <c r="D10" t="n">
         <v>3.26530612244898</v>
@@ -982,55 +1057,64 @@
         <v>2.333333333333333</v>
       </c>
       <c r="F10" t="n">
-        <v>0.02862713503093027</v>
-      </c>
-      <c r="G10" t="inlineStr">
+        <v>0.05725427006186055</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.8588140509279083</v>
+      </c>
+      <c r="H10" t="inlineStr">
         <is>
           <t>(0.46598639455782315, 'medium')</t>
         </is>
       </c>
-      <c r="H10" t="n">
+      <c r="I10" t="n">
         <v>3.25</v>
       </c>
-      <c r="I10" t="n">
+      <c r="J10" t="n">
         <v>3</v>
       </c>
-      <c r="J10" t="n">
-        <v>0.1895748632131497</v>
-      </c>
-      <c r="K10" t="inlineStr">
+      <c r="K10" t="n">
+        <v>0.3791497264262994</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1</v>
+      </c>
+      <c r="M10" t="inlineStr">
         <is>
           <t>(0.15535714285714286, 'small')</t>
         </is>
       </c>
-      <c r="L10" t="n">
-        <v>3.058823529411764</v>
-      </c>
-      <c r="M10" t="n">
-        <v>3.210526315789474</v>
-      </c>
       <c r="N10" t="n">
-        <v>0.6914177867990292</v>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>(-0.0804953560371517, 'negligible')</t>
+        <v>3.1875</v>
+      </c>
+      <c r="O10" t="n">
+        <v>3</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0.6284753216771641</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1</v>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>(0.1130952380952381, 'negligible')</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Engenharia de Requisitos de Segurança</t>
+          <t>Security Requirements Engineering</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>facilidade</t>
+          <t>Ease of use</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2.421686746987952</v>
+        <v>3.19047619047619</v>
       </c>
       <c r="D11" t="n">
         <v>3.264150943396226</v>
@@ -1039,55 +1123,64 @@
         <v>2.8</v>
       </c>
       <c r="F11" t="n">
-        <v>0.07578596068194351</v>
-      </c>
-      <c r="G11" t="inlineStr">
+        <v>0.151571921363887</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1</v>
+      </c>
+      <c r="H11" t="inlineStr">
         <is>
           <t>(0.27358490566037735, 'small')</t>
         </is>
       </c>
-      <c r="H11" t="n">
+      <c r="I11" t="n">
         <v>3.276595744680851</v>
       </c>
-      <c r="I11" t="n">
+      <c r="J11" t="n">
         <v>3.142857142857143</v>
       </c>
-      <c r="J11" t="n">
-        <v>0.3014665222542774</v>
-      </c>
-      <c r="K11" t="inlineStr">
+      <c r="K11" t="n">
+        <v>0.6029330445085548</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1</v>
+      </c>
+      <c r="M11" t="inlineStr">
         <is>
           <t>(0.08814589665653495, 'negligible')</t>
         </is>
       </c>
-      <c r="L11" t="n">
-        <v>3</v>
-      </c>
-      <c r="M11" t="n">
-        <v>3.292682926829268</v>
-      </c>
       <c r="N11" t="n">
-        <v>0.8918861349563805</v>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>(-0.17849223946784923, 'small')</t>
+        <v>3.1875</v>
+      </c>
+      <c r="O11" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0.9183380634995262</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1</v>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>(-0.018055555555555554, 'negligible')</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Codificação Segura</t>
+          <t>Secure Coding</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>facilidade</t>
+          <t>Ease of use</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>2.590361445783132</v>
+        <v>3.307692307692308</v>
       </c>
       <c r="D12" t="n">
         <v>3.411764705882353</v>
@@ -1096,55 +1189,64 @@
         <v>2.928571428571428</v>
       </c>
       <c r="F12" t="n">
-        <v>0.06216385160055331</v>
-      </c>
-      <c r="G12" t="inlineStr">
+        <v>0.1243277032011066</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H12" t="inlineStr">
         <is>
           <t>(0.2619047619047619, 'small')</t>
         </is>
       </c>
-      <c r="H12" t="n">
+      <c r="I12" t="n">
         <v>3.36</v>
       </c>
-      <c r="I12" t="n">
+      <c r="J12" t="n">
         <v>3.230769230769231</v>
       </c>
-      <c r="J12" t="n">
-        <v>0.395973395721591</v>
-      </c>
-      <c r="K12" t="inlineStr">
+      <c r="K12" t="n">
+        <v>0.7919467914431819</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1</v>
+      </c>
+      <c r="M12" t="inlineStr">
         <is>
           <t>(0.047692307692307694, 'negligible')</t>
         </is>
       </c>
-      <c r="L12" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="M12" t="n">
-        <v>3.4</v>
-      </c>
       <c r="N12" t="n">
-        <v>0.8536943490739011</v>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>(-0.15777777777777777, 'small')</t>
+        <v>3.347826086956522</v>
+      </c>
+      <c r="O12" t="n">
+        <v>3.210526315789474</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0.5907781182630852</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1</v>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>(0.08352402745995423, 'negligible')</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Resposta Emergencial ao Código</t>
+          <t>Emergency Codebase Response</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>facilidade</t>
+          <t>Ease of use</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>2.012048192771084</v>
+        <v>3.036363636363637</v>
       </c>
       <c r="D13" t="n">
         <v>3.065217391304348</v>
@@ -1153,55 +1255,64 @@
         <v>2.888888888888889</v>
       </c>
       <c r="F13" t="n">
-        <v>0.4060663243508396</v>
-      </c>
-      <c r="G13" t="inlineStr">
+        <v>0.8121326487016791</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H13" t="inlineStr">
         <is>
           <t>(0.050724637681159424, 'negligible')</t>
         </is>
       </c>
-      <c r="H13" t="n">
+      <c r="I13" t="n">
         <v>3.095238095238095</v>
       </c>
-      <c r="I13" t="n">
+      <c r="J13" t="n">
         <v>2.846153846153846</v>
       </c>
-      <c r="J13" t="n">
-        <v>0.3702702533186408</v>
-      </c>
-      <c r="K13" t="inlineStr">
+      <c r="K13" t="n">
+        <v>0.7405405066372817</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1</v>
+      </c>
+      <c r="M13" t="inlineStr">
         <is>
           <t>(0.06043956043956044, 'negligible')</t>
         </is>
       </c>
-      <c r="L13" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="M13" t="n">
-        <v>3.219512195121951</v>
-      </c>
       <c r="N13" t="n">
-        <v>0.9846057696705625</v>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>(-0.3710801393728223, 'medium')</t>
+        <v>2.953488372093023</v>
+      </c>
+      <c r="O13" t="n">
+        <v>3.333333333333333</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0.2373832862965047</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1</v>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>(-0.21705426356589147, 'small')</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Configurações e Gerenciamento de Segurança</t>
+          <t>Security Configuration and Management</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>facilidade</t>
+          <t>Ease of use</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>2.63855421686747</v>
+        <v>3.318181818181818</v>
       </c>
       <c r="D14" t="n">
         <v>3.377358490566038</v>
@@ -1210,55 +1321,64 @@
         <v>3.076923076923077</v>
       </c>
       <c r="F14" t="n">
-        <v>0.1745822268591613</v>
-      </c>
-      <c r="G14" t="inlineStr">
+        <v>0.3491644537183226</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1</v>
+      </c>
+      <c r="H14" t="inlineStr">
         <is>
           <t>(0.16400580551523947, 'small')</t>
         </is>
       </c>
-      <c r="H14" t="n">
+      <c r="I14" t="n">
         <v>3.411764705882353</v>
       </c>
-      <c r="I14" t="n">
+      <c r="J14" t="n">
         <v>3</v>
       </c>
-      <c r="J14" t="n">
-        <v>0.1091163358768145</v>
-      </c>
-      <c r="K14" t="inlineStr">
+      <c r="K14" t="n">
+        <v>0.218232671753629</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1</v>
+      </c>
+      <c r="M14" t="inlineStr">
         <is>
           <t>(0.21008403361344538, 'small')</t>
         </is>
       </c>
-      <c r="L14" t="n">
-        <v>3.380952380952381</v>
-      </c>
-      <c r="M14" t="n">
-        <v>3.288888888888889</v>
-      </c>
       <c r="N14" t="n">
-        <v>0.3958554515677144</v>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>(0.04021164021164021, 'negligible')</t>
+        <v>3.3125</v>
+      </c>
+      <c r="O14" t="n">
+        <v>3.333333333333333</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0.9880886090909259</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>1</v>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>(-0.003472222222222222, 'negligible')</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Monitoramento de Eventos de Segurança</t>
+          <t>Monitoring for Security Events</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>facilidade</t>
+          <t>Ease of use</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>2.506024096385542</v>
+        <v>3.25</v>
       </c>
       <c r="D15" t="n">
         <v>3.24</v>
@@ -1267,55 +1387,64 @@
         <v>3.285714285714286</v>
       </c>
       <c r="F15" t="n">
-        <v>0.5171505464736408</v>
-      </c>
-      <c r="G15" t="inlineStr">
+        <v>0.9794152848356945</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H15" t="inlineStr">
         <is>
           <t>(-0.005714285714285714, 'negligible')</t>
         </is>
       </c>
-      <c r="H15" t="n">
+      <c r="I15" t="n">
         <v>3.333333333333333</v>
       </c>
-      <c r="I15" t="n">
+      <c r="J15" t="n">
         <v>3</v>
       </c>
-      <c r="J15" t="n">
-        <v>0.2731523645105361</v>
-      </c>
-      <c r="K15" t="inlineStr">
+      <c r="K15" t="n">
+        <v>0.5463047290210723</v>
+      </c>
+      <c r="L15" t="n">
+        <v>1</v>
+      </c>
+      <c r="M15" t="inlineStr">
         <is>
           <t>(0.10267857142857142, 'negligible')</t>
         </is>
       </c>
-      <c r="L15" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="M15" t="n">
-        <v>3.113636363636364</v>
-      </c>
       <c r="N15" t="n">
-        <v>0.1028141268689159</v>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>(0.18863636363636363, 'small')</t>
+        <v>3.088888888888889</v>
+      </c>
+      <c r="O15" t="n">
+        <v>3.631578947368421</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0.0799500310050434</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1</v>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>(-0.26432748538011697, 'small')</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Auditorias de Segurança Externas</t>
+          <t>Undergoing External Security Audits</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>facilidade</t>
+          <t>Ease of use</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>2.19277108433735</v>
+        <v>3.137931034482759</v>
       </c>
       <c r="D16" t="n">
         <v>3.224489795918367</v>
@@ -1324,55 +1453,64 @@
         <v>2.666666666666667</v>
       </c>
       <c r="F16" t="n">
-        <v>0.09089089967232311</v>
-      </c>
-      <c r="G16" t="inlineStr">
+        <v>0.1817817993446462</v>
+      </c>
+      <c r="G16" t="n">
+        <v>1</v>
+      </c>
+      <c r="H16" t="inlineStr">
         <is>
           <t>(0.2766439909297052, 'small')</t>
         </is>
       </c>
-      <c r="H16" t="n">
+      <c r="I16" t="n">
         <v>3.177777777777778</v>
       </c>
-      <c r="I16" t="n">
+      <c r="J16" t="n">
         <v>3</v>
       </c>
-      <c r="J16" t="n">
-        <v>0.3475074753753823</v>
-      </c>
-      <c r="K16" t="inlineStr">
+      <c r="K16" t="n">
+        <v>0.6950149507507646</v>
+      </c>
+      <c r="L16" t="n">
+        <v>1</v>
+      </c>
+      <c r="M16" t="inlineStr">
         <is>
           <t>(0.07407407407407407, 'negligible')</t>
         </is>
       </c>
-      <c r="L16" t="n">
-        <v>3.166666666666667</v>
-      </c>
-      <c r="M16" t="n">
-        <v>3.125</v>
-      </c>
       <c r="N16" t="n">
-        <v>0.37793159953203</v>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>(0.05138888888888889, 'negligible')</t>
+        <v>3.25</v>
+      </c>
+      <c r="O16" t="n">
+        <v>2.785714285714286</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0.2248080540685446</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>1</v>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>(0.21266233766233766, 'small')</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Segurança da Cadeia de Suprimentos de Software</t>
+          <t>Software Supply Chain Security</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>facilidade</t>
+          <t>Ease of use</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>2.144578313253012</v>
+        <v>3.068965517241379</v>
       </c>
       <c r="D17" t="n">
         <v>3.02</v>
@@ -1381,55 +1519,64 @@
         <v>3.375</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7855416490168075</v>
-      </c>
-      <c r="G17" t="inlineStr">
+        <v>0.4426174917637538</v>
+      </c>
+      <c r="G17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H17" t="inlineStr">
         <is>
           <t>(-0.1675, 'small')</t>
         </is>
       </c>
-      <c r="H17" t="n">
+      <c r="I17" t="n">
         <v>3.177777777777778</v>
       </c>
-      <c r="I17" t="n">
+      <c r="J17" t="n">
         <v>2.666666666666667</v>
       </c>
-      <c r="J17" t="n">
-        <v>0.1425141583880039</v>
-      </c>
-      <c r="K17" t="inlineStr">
+      <c r="K17" t="n">
+        <v>0.2850283167760077</v>
+      </c>
+      <c r="L17" t="n">
+        <v>1</v>
+      </c>
+      <c r="M17" t="inlineStr">
         <is>
           <t>(0.19814814814814816, 'small')</t>
         </is>
       </c>
-      <c r="L17" t="n">
-        <v>3</v>
-      </c>
-      <c r="M17" t="n">
-        <v>3.097560975609756</v>
-      </c>
       <c r="N17" t="n">
-        <v>0.6509020265525297</v>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>(-0.06169296987087518, 'negligible')</t>
+        <v>3.065217391304348</v>
+      </c>
+      <c r="O17" t="n">
+        <v>3.083333333333333</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0.9605100715942132</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1</v>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>(-0.010869565217391304, 'negligible')</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Revisão de Código</t>
+          <t>Code Review</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>efetividade</t>
+          <t>Effectiveness</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>3.819277108433735</v>
+        <v>4.226666666666667</v>
       </c>
       <c r="D18" t="n">
         <v>4.2</v>
@@ -1438,55 +1585,64 @@
         <v>4.333333333333333</v>
       </c>
       <c r="F18" t="n">
-        <v>0.6690476158930665</v>
-      </c>
-      <c r="G18" t="inlineStr">
+        <v>0.6723334496156849</v>
+      </c>
+      <c r="G18" t="n">
+        <v>1</v>
+      </c>
+      <c r="H18" t="inlineStr">
         <is>
           <t>(-0.06666666666666667, 'negligible')</t>
         </is>
       </c>
-      <c r="H18" t="n">
+      <c r="I18" t="n">
         <v>4.189655172413793</v>
       </c>
-      <c r="I18" t="n">
+      <c r="J18" t="n">
         <v>4.333333333333333</v>
       </c>
-      <c r="J18" t="n">
-        <v>0.7830407366509105</v>
-      </c>
-      <c r="K18" t="inlineStr">
+      <c r="K18" t="n">
+        <v>0.4426418920079739</v>
+      </c>
+      <c r="L18" t="n">
+        <v>1</v>
+      </c>
+      <c r="M18" t="inlineStr">
         <is>
           <t>(-0.1206896551724138, 'negligible')</t>
         </is>
       </c>
-      <c r="L18" t="n">
-        <v>4</v>
-      </c>
-      <c r="M18" t="n">
-        <v>4.326923076923077</v>
-      </c>
       <c r="N18" t="n">
-        <v>0.966244619991062</v>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>(-0.24498327759197325, 'small')</t>
+        <v>4.137254901960785</v>
+      </c>
+      <c r="O18" t="n">
+        <v>4.416666666666667</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0.2960254266257267</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>1</v>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>(-0.13970588235294118, 'negligible')</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Modelagem de Ameaças</t>
+          <t>Threat Modeling</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>efetividade</t>
+          <t>Effectiveness</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>3.240963855421687</v>
+        <v>4.138461538461539</v>
       </c>
       <c r="D19" t="n">
         <v>4.181818181818182</v>
@@ -1495,55 +1651,64 @@
         <v>3.9</v>
       </c>
       <c r="F19" t="n">
-        <v>0.2152810391892057</v>
-      </c>
-      <c r="G19" t="inlineStr">
+        <v>0.4305620783784114</v>
+      </c>
+      <c r="G19" t="n">
+        <v>1</v>
+      </c>
+      <c r="H19" t="inlineStr">
         <is>
           <t>(0.14909090909090908, 'small')</t>
         </is>
       </c>
-      <c r="H19" t="n">
+      <c r="I19" t="n">
         <v>4.22</v>
       </c>
-      <c r="I19" t="n">
+      <c r="J19" t="n">
         <v>3.857142857142857</v>
       </c>
-      <c r="J19" t="n">
-        <v>0.2220052416458971</v>
-      </c>
-      <c r="K19" t="inlineStr">
+      <c r="K19" t="n">
+        <v>0.4440104832917943</v>
+      </c>
+      <c r="L19" t="n">
+        <v>1</v>
+      </c>
+      <c r="M19" t="inlineStr">
         <is>
           <t>(0.12714285714285714, 'negligible')</t>
         </is>
       </c>
-      <c r="L19" t="n">
-        <v>3.941176470588236</v>
-      </c>
-      <c r="M19" t="n">
-        <v>4.208333333333333</v>
-      </c>
       <c r="N19" t="n">
-        <v>0.9440661980382037</v>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>(-0.2426470588235294, 'small')</t>
+        <v>4.12</v>
+      </c>
+      <c r="O19" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0.6953045223361749</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>1</v>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>(-0.064, 'negligible')</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Identificação de Casos de Abuso/Mau Uso</t>
+          <t>Identifying Abuse/Misuse Cases</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>efetividade</t>
+          <t>Effectiveness</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>3.192771084337349</v>
+        <v>3.840579710144927</v>
       </c>
       <c r="D20" t="n">
         <v>3.824561403508772</v>
@@ -1552,55 +1717,64 @@
         <v>3.916666666666667</v>
       </c>
       <c r="F20" t="n">
-        <v>0.5915044232504775</v>
-      </c>
-      <c r="G20" t="inlineStr">
+        <v>0.8298555275884725</v>
+      </c>
+      <c r="G20" t="n">
+        <v>1</v>
+      </c>
+      <c r="H20" t="inlineStr">
         <is>
           <t>(-0.039473684210526314, 'negligible')</t>
         </is>
       </c>
-      <c r="H20" t="n">
+      <c r="I20" t="n">
         <v>3.888888888888889</v>
       </c>
-      <c r="I20" t="n">
+      <c r="J20" t="n">
         <v>3.642857142857143</v>
       </c>
-      <c r="J20" t="n">
-        <v>0.3258656311287144</v>
-      </c>
-      <c r="K20" t="inlineStr">
+      <c r="K20" t="n">
+        <v>0.6517312622574287</v>
+      </c>
+      <c r="L20" t="n">
+        <v>1</v>
+      </c>
+      <c r="M20" t="inlineStr">
         <is>
           <t>(0.07671957671957672, 'negligible')</t>
         </is>
       </c>
-      <c r="L20" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="M20" t="n">
-        <v>3.897959183673469</v>
-      </c>
       <c r="N20" t="n">
-        <v>0.8243702144896332</v>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>(-0.13673469387755102, 'negligible')</t>
+        <v>3.803921568627451</v>
+      </c>
+      <c r="O20" t="n">
+        <v>3.944444444444445</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0.5301306202344216</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>1</v>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>(-0.09694989106753812, 'negligible')</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Análise de Riscos Arquiteturais</t>
+          <t>Architectural Risk Analysis</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>efetividade</t>
+          <t>Effectiveness</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>3.578313253012048</v>
+        <v>4.183098591549296</v>
       </c>
       <c r="D21" t="n">
         <v>4.137931034482759</v>
@@ -1609,55 +1783,64 @@
         <v>4.384615384615385</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7387103205093204</v>
-      </c>
-      <c r="G21" t="inlineStr">
+        <v>0.5330282023845776</v>
+      </c>
+      <c r="G21" t="n">
+        <v>1</v>
+      </c>
+      <c r="H21" t="inlineStr">
         <is>
           <t>(-0.10477453580901856, 'negligible')</t>
         </is>
       </c>
-      <c r="H21" t="n">
+      <c r="I21" t="n">
         <v>4.181818181818182</v>
       </c>
-      <c r="I21" t="n">
+      <c r="J21" t="n">
         <v>4.2</v>
       </c>
-      <c r="J21" t="n">
-        <v>0.6888950411544035</v>
-      </c>
-      <c r="K21" t="inlineStr">
+      <c r="K21" t="n">
+        <v>0.633131977730246</v>
+      </c>
+      <c r="L21" t="n">
+        <v>1</v>
+      </c>
+      <c r="M21" t="inlineStr">
         <is>
           <t>(-0.07636363636363637, 'negligible')</t>
         </is>
       </c>
-      <c r="L21" t="n">
-        <v>4.272727272727272</v>
-      </c>
-      <c r="M21" t="n">
-        <v>4.142857142857143</v>
-      </c>
       <c r="N21" t="n">
-        <v>0.4441855425932394</v>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>(0.02040816326530612, 'negligible')</t>
+        <v>4.076923076923077</v>
+      </c>
+      <c r="O21" t="n">
+        <v>4.473684210526316</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0.1245349420991351</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>1</v>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>(-0.2236842105263158, 'small')</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Testes de Penetração</t>
+          <t>Penetration Testing</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>efetividade</t>
+          <t>Effectiveness</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>3.63855421686747</v>
+        <v>4.376811594202898</v>
       </c>
       <c r="D22" t="n">
         <v>4.448275862068965</v>
@@ -1666,55 +1849,64 @@
         <v>4</v>
       </c>
       <c r="F22" t="n">
-        <v>0.05579045652795837</v>
-      </c>
-      <c r="G22" t="inlineStr">
+        <v>0.1115809130559167</v>
+      </c>
+      <c r="G22" t="n">
+        <v>1</v>
+      </c>
+      <c r="H22" t="inlineStr">
         <is>
           <t>(0.2727272727272727, 'small')</t>
         </is>
       </c>
-      <c r="H22" t="n">
+      <c r="I22" t="n">
         <v>4.39622641509434</v>
       </c>
-      <c r="I22" t="n">
+      <c r="J22" t="n">
         <v>4.285714285714286</v>
       </c>
-      <c r="J22" t="n">
-        <v>0.320113998552045</v>
-      </c>
-      <c r="K22" t="inlineStr">
+      <c r="K22" t="n">
+        <v>0.6402279971040901</v>
+      </c>
+      <c r="L22" t="n">
+        <v>1</v>
+      </c>
+      <c r="M22" t="inlineStr">
         <is>
           <t>(0.07412398921832884, 'negligible')</t>
         </is>
       </c>
-      <c r="L22" t="n">
-        <v>4.318181818181818</v>
-      </c>
-      <c r="M22" t="n">
-        <v>4.404255319148936</v>
-      </c>
       <c r="N22" t="n">
-        <v>0.7928558977857513</v>
-      </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>(-0.10831721470019343, 'negligible')</t>
+        <v>4.377358490566038</v>
+      </c>
+      <c r="O22" t="n">
+        <v>4.375</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0.7862081605474124</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>1</v>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>(-0.041273584905660375, 'negligible')</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Gerenciamento de Riscos</t>
+          <t>Risk Management</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>efetividade</t>
+          <t>Effectiveness</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>3.542168674698795</v>
+        <v>4.260869565217392</v>
       </c>
       <c r="D23" t="n">
         <v>4.285714285714286</v>
@@ -1723,55 +1915,64 @@
         <v>4.153846153846154</v>
       </c>
       <c r="F23" t="n">
-        <v>0.0996589630080576</v>
-      </c>
-      <c r="G23" t="inlineStr">
+        <v>0.1993179260161152</v>
+      </c>
+      <c r="G23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H23" t="inlineStr">
         <is>
           <t>(0.21153846153846154, 'small')</t>
         </is>
       </c>
-      <c r="H23" t="n">
+      <c r="I23" t="n">
         <v>4.264150943396227</v>
       </c>
-      <c r="I23" t="n">
+      <c r="J23" t="n">
         <v>4.214285714285714</v>
       </c>
-      <c r="J23" t="n">
-        <v>0.6255138365626866</v>
-      </c>
-      <c r="K23" t="inlineStr">
+      <c r="K23" t="n">
+        <v>0.7617733410142316</v>
+      </c>
+      <c r="L23" t="n">
+        <v>1</v>
+      </c>
+      <c r="M23" t="inlineStr">
         <is>
           <t>(-0.04986522911051213, 'negligible')</t>
         </is>
       </c>
-      <c r="L23" t="n">
-        <v>4</v>
-      </c>
-      <c r="M23" t="n">
-        <v>4.375</v>
-      </c>
       <c r="N23" t="n">
-        <v>0.9424348147016396</v>
-      </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>(-0.21825396825396826, 'small')</t>
+        <v>4.183673469387755</v>
+      </c>
+      <c r="O23" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0.4830915766666114</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>1</v>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>(-0.1, 'negligible')</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Gerenciamento de Vulnerabilidades</t>
+          <t>Vulnerability Management</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>efetividade</t>
+          <t>Effectiveness</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>3.783132530120481</v>
+        <v>4.301369863013698</v>
       </c>
       <c r="D24" t="n">
         <v>4.288135593220339</v>
@@ -1780,55 +1981,64 @@
         <v>4.357142857142857</v>
       </c>
       <c r="F24" t="n">
-        <v>0.4050097612986614</v>
-      </c>
-      <c r="G24" t="inlineStr">
+        <v>0.8100195225973228</v>
+      </c>
+      <c r="G24" t="n">
+        <v>1</v>
+      </c>
+      <c r="H24" t="inlineStr">
         <is>
           <t>(0.0387409200968523, 'negligible')</t>
         </is>
       </c>
-      <c r="H24" t="n">
+      <c r="I24" t="n">
         <v>4.298245614035087</v>
       </c>
-      <c r="I24" t="n">
+      <c r="J24" t="n">
         <v>4.214285714285714</v>
       </c>
-      <c r="J24" t="n">
-        <v>0.348392608100787</v>
-      </c>
-      <c r="K24" t="inlineStr">
+      <c r="K24" t="n">
+        <v>0.696785216201574</v>
+      </c>
+      <c r="L24" t="n">
+        <v>1</v>
+      </c>
+      <c r="M24" t="inlineStr">
         <is>
           <t>(0.06265664160401002, 'negligible')</t>
         </is>
       </c>
-      <c r="L24" t="n">
-        <v>4.181818181818182</v>
-      </c>
-      <c r="M24" t="n">
-        <v>4.352941176470588</v>
-      </c>
       <c r="N24" t="n">
-        <v>0.8172442457622354</v>
-      </c>
-      <c r="O24" t="inlineStr">
-        <is>
-          <t>(-0.12032085561497326, 'negligible')</t>
+        <v>4.173076923076923</v>
+      </c>
+      <c r="O24" t="n">
+        <v>4.619047619047619</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0.08423864666411766</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>1</v>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>(-0.23534798534798534, 'small')</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Testes de Segurança Manuais/Automatizados</t>
+          <t>Manual/Automated Security Testing</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>efetividade</t>
+          <t>Effectiveness</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>3.662650602409639</v>
+        <v>4.164383561643835</v>
       </c>
       <c r="D25" t="n">
         <v>4.169491525423729</v>
@@ -1837,55 +2047,64 @@
         <v>4.142857142857143</v>
       </c>
       <c r="F25" t="n">
-        <v>0.2916815135042219</v>
-      </c>
-      <c r="G25" t="inlineStr">
+        <v>0.5833630270084438</v>
+      </c>
+      <c r="G25" t="n">
+        <v>1</v>
+      </c>
+      <c r="H25" t="inlineStr">
         <is>
           <t>(0.08958837772397095, 'negligible')</t>
         </is>
       </c>
-      <c r="H25" t="n">
+      <c r="I25" t="n">
         <v>4.071428571428571</v>
       </c>
-      <c r="I25" t="n">
+      <c r="J25" t="n">
         <v>4.4</v>
       </c>
-      <c r="J25" t="n">
-        <v>0.869003811087273</v>
-      </c>
-      <c r="K25" t="inlineStr">
+      <c r="K25" t="n">
+        <v>0.2684504074112056</v>
+      </c>
+      <c r="L25" t="n">
+        <v>1</v>
+      </c>
+      <c r="M25" t="inlineStr">
         <is>
           <t>(-0.1761904761904762, 'small')</t>
         </is>
       </c>
-      <c r="L25" t="n">
-        <v>4.083333333333333</v>
-      </c>
-      <c r="M25" t="n">
-        <v>4.204081632653061</v>
-      </c>
       <c r="N25" t="n">
-        <v>0.611548930352069</v>
-      </c>
-      <c r="O25" t="inlineStr">
-        <is>
-          <t>(-0.03741496598639456, 'negligible')</t>
+        <v>4.058823529411764</v>
+      </c>
+      <c r="O25" t="n">
+        <v>4.409090909090909</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0.2230691561358596</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>1</v>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>(-0.16934046345811052, 'small')</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Execução de Testes Fuzz</t>
+          <t>Performing Fuzz Testing</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>efetividade</t>
+          <t>Effectiveness</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>2.385542168674699</v>
+        <v>3.35593220338983</v>
       </c>
       <c r="D26" t="n">
         <v>3.384615384615385</v>
@@ -1894,55 +2113,64 @@
         <v>3.142857142857143</v>
       </c>
       <c r="F26" t="n">
-        <v>0.2810756282237484</v>
-      </c>
-      <c r="G26" t="inlineStr">
+        <v>0.5621512564474969</v>
+      </c>
+      <c r="G26" t="n">
+        <v>1</v>
+      </c>
+      <c r="H26" t="inlineStr">
         <is>
           <t>(0.1346153846153846, 'negligible')</t>
         </is>
       </c>
-      <c r="H26" t="n">
+      <c r="I26" t="n">
         <v>3.348837209302326</v>
       </c>
-      <c r="I26" t="n">
+      <c r="J26" t="n">
         <v>3.4</v>
       </c>
-      <c r="J26" t="n">
-        <v>0.5725255127678833</v>
-      </c>
-      <c r="K26" t="inlineStr">
+      <c r="K26" t="n">
+        <v>0.8693164097090573</v>
+      </c>
+      <c r="L26" t="n">
+        <v>1</v>
+      </c>
+      <c r="M26" t="inlineStr">
         <is>
           <t>(-0.02945736434108527, 'negligible')</t>
         </is>
       </c>
-      <c r="L26" t="n">
-        <v>3.294117647058823</v>
-      </c>
-      <c r="M26" t="n">
-        <v>3.380952380952381</v>
-      </c>
       <c r="N26" t="n">
-        <v>0.6349129355114269</v>
-      </c>
-      <c r="O26" t="inlineStr">
-        <is>
-          <t>(-0.0546218487394958, 'negligible')</t>
+        <v>3.270833333333333</v>
+      </c>
+      <c r="O26" t="n">
+        <v>3.727272727272727</v>
+      </c>
+      <c r="P26" t="n">
+        <v>0.2788604702258664</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>1</v>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>(-0.20643939393939395, 'small')</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Engenharia de Requisitos de Segurança</t>
+          <t>Security Requirements Engineering</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>efetividade</t>
+          <t>Effectiveness</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>3.481927710843373</v>
+        <v>4.188405797101449</v>
       </c>
       <c r="D27" t="n">
         <v>4.142857142857143</v>
@@ -1951,55 +2179,64 @@
         <v>4.384615384615385</v>
       </c>
       <c r="F27" t="n">
-        <v>0.8392598895185552</v>
-      </c>
-      <c r="G27" t="inlineStr">
+        <v>0.3296113679589989</v>
+      </c>
+      <c r="G27" t="n">
+        <v>1</v>
+      </c>
+      <c r="H27" t="inlineStr">
         <is>
           <t>(-0.16346153846153846, 'small')</t>
         </is>
       </c>
-      <c r="H27" t="n">
+      <c r="I27" t="n">
         <v>4.235294117647059</v>
       </c>
-      <c r="I27" t="n">
+      <c r="J27" t="n">
         <v>4.0625</v>
       </c>
-      <c r="J27" t="n">
-        <v>0.4059068807824879</v>
-      </c>
-      <c r="K27" t="inlineStr">
+      <c r="K27" t="n">
+        <v>0.8118137615649758</v>
+      </c>
+      <c r="L27" t="n">
+        <v>1</v>
+      </c>
+      <c r="M27" t="inlineStr">
         <is>
           <t>(0.03799019607843137, 'negligible')</t>
         </is>
       </c>
-      <c r="L27" t="n">
-        <v>4</v>
-      </c>
-      <c r="M27" t="n">
-        <v>4.276595744680851</v>
-      </c>
       <c r="N27" t="n">
-        <v>0.9559367762000509</v>
-      </c>
-      <c r="O27" t="inlineStr">
-        <is>
-          <t>(-0.2369439071566731, 'small')</t>
+        <v>4.14</v>
+      </c>
+      <c r="O27" t="n">
+        <v>4.315789473684211</v>
+      </c>
+      <c r="P27" t="n">
+        <v>0.4651033646265303</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>1</v>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>(-0.10736842105263159, 'negligible')</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Codificação Segura</t>
+          <t>Secure Coding</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>efetividade</t>
+          <t>Effectiveness</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>3.481927710843373</v>
+        <v>4.378787878787879</v>
       </c>
       <c r="D28" t="n">
         <v>4.346153846153846</v>
@@ -2008,55 +2245,64 @@
         <v>4.5</v>
       </c>
       <c r="F28" t="n">
-        <v>0.5910276643644787</v>
-      </c>
-      <c r="G28" t="inlineStr">
+        <v>0.8317306786873775</v>
+      </c>
+      <c r="G28" t="n">
+        <v>1</v>
+      </c>
+      <c r="H28" t="inlineStr">
         <is>
           <t>(-0.034340659340659344, 'negligible')</t>
         </is>
       </c>
-      <c r="H28" t="n">
+      <c r="I28" t="n">
         <v>4.365384615384615</v>
       </c>
-      <c r="I28" t="n">
+      <c r="J28" t="n">
         <v>4.416666666666667</v>
       </c>
-      <c r="J28" t="n">
-        <v>0.7517386289770782</v>
-      </c>
-      <c r="K28" t="inlineStr">
+      <c r="K28" t="n">
+        <v>0.5089051886039414</v>
+      </c>
+      <c r="L28" t="n">
+        <v>1</v>
+      </c>
+      <c r="M28" t="inlineStr">
         <is>
           <t>(-0.11057692307692307, 'negligible')</t>
         </is>
       </c>
-      <c r="L28" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="M28" t="n">
-        <v>4.521739130434782</v>
-      </c>
       <c r="N28" t="n">
-        <v>0.9905355534400277</v>
-      </c>
-      <c r="O28" t="inlineStr">
-        <is>
-          <t>(-0.32282608695652176, 'small')</t>
+        <v>4.288888888888889</v>
+      </c>
+      <c r="O28" t="n">
+        <v>4.571428571428571</v>
+      </c>
+      <c r="P28" t="n">
+        <v>0.2835582987143855</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>1</v>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>(-0.14708994708994708, 'small')</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Resposta Emergencial ao Código</t>
+          <t>Emergency Codebase Response</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>efetividade</t>
+          <t>Effectiveness</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>2.590361445783132</v>
+        <v>3.706896551724138</v>
       </c>
       <c r="D29" t="n">
         <v>3.833333333333333</v>
@@ -2065,55 +2311,64 @@
         <v>3.1</v>
       </c>
       <c r="F29" t="n">
-        <v>0.05405883845665009</v>
-      </c>
-      <c r="G29" t="inlineStr">
+        <v>0.1081176769133002</v>
+      </c>
+      <c r="G29" t="n">
+        <v>1</v>
+      </c>
+      <c r="H29" t="inlineStr">
         <is>
           <t>(0.3145833333333333, 'small')</t>
         </is>
       </c>
-      <c r="H29" t="n">
+      <c r="I29" t="n">
         <v>3.717391304347826</v>
       </c>
-      <c r="I29" t="n">
+      <c r="J29" t="n">
         <v>3.666666666666667</v>
       </c>
-      <c r="J29" t="n">
-        <v>0.468155400853318</v>
-      </c>
-      <c r="K29" t="inlineStr">
+      <c r="K29" t="n">
+        <v>0.9363108017066361</v>
+      </c>
+      <c r="L29" t="n">
+        <v>1</v>
+      </c>
+      <c r="M29" t="inlineStr">
         <is>
           <t>(0.016304347826086956, 'negligible')</t>
         </is>
       </c>
-      <c r="L29" t="n">
-        <v>3.357142857142857</v>
-      </c>
-      <c r="M29" t="n">
-        <v>3.818181818181818</v>
-      </c>
       <c r="N29" t="n">
-        <v>0.8974250048320671</v>
-      </c>
-      <c r="O29" t="inlineStr">
-        <is>
-          <t>(-0.2159090909090909, 'small')</t>
+        <v>3.627906976744186</v>
+      </c>
+      <c r="O29" t="n">
+        <v>3.933333333333333</v>
+      </c>
+      <c r="P29" t="n">
+        <v>0.4108554198121563</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>1</v>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>(-0.13953488372093023, 'negligible')</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Configurações e Gerenciamento de Segurança</t>
+          <t>Security Configuration and Management</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>efetividade</t>
+          <t>Effectiveness</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>3.253012048192771</v>
+        <v>4.090909090909091</v>
       </c>
       <c r="D30" t="n">
         <v>4.076923076923077</v>
@@ -2122,55 +2377,64 @@
         <v>4.142857142857143</v>
       </c>
       <c r="F30" t="n">
-        <v>0.6402773853482063</v>
-      </c>
-      <c r="G30" t="inlineStr">
+        <v>0.7319796563207985</v>
+      </c>
+      <c r="G30" t="n">
+        <v>1</v>
+      </c>
+      <c r="H30" t="inlineStr">
         <is>
           <t>(-0.057692307692307696, 'negligible')</t>
         </is>
       </c>
-      <c r="H30" t="n">
+      <c r="I30" t="n">
         <v>4.134615384615385</v>
       </c>
-      <c r="I30" t="n">
+      <c r="J30" t="n">
         <v>4</v>
       </c>
-      <c r="J30" t="n">
-        <v>0.2643001421791115</v>
-      </c>
-      <c r="K30" t="inlineStr">
+      <c r="K30" t="n">
+        <v>0.5286002843582229</v>
+      </c>
+      <c r="L30" t="n">
+        <v>1</v>
+      </c>
+      <c r="M30" t="inlineStr">
         <is>
           <t>(0.10798816568047337, 'negligible')</t>
         </is>
       </c>
-      <c r="L30" t="n">
-        <v>3.789473684210526</v>
-      </c>
-      <c r="M30" t="n">
-        <v>4.212765957446808</v>
-      </c>
       <c r="N30" t="n">
-        <v>0.9698129641867167</v>
-      </c>
-      <c r="O30" t="inlineStr">
-        <is>
-          <t>(-0.2777155655095185, 'small')</t>
+        <v>4.022222222222222</v>
+      </c>
+      <c r="O30" t="n">
+        <v>4.238095238095238</v>
+      </c>
+      <c r="P30" t="n">
+        <v>0.2877233495281559</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>1</v>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>(-0.1544973544973545, 'small')</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Monitoramento de Eventos de Segurança</t>
+          <t>Monitoring for Security Events</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>efetividade</t>
+          <t>Effectiveness</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>3.566265060240964</v>
+        <v>4.417910447761194</v>
       </c>
       <c r="D31" t="n">
         <v>4.423076923076923</v>
@@ -2179,55 +2443,64 @@
         <v>4.4</v>
       </c>
       <c r="F31" t="n">
-        <v>0.4330267779428367</v>
-      </c>
-      <c r="G31" t="inlineStr">
+        <v>0.8660535558856735</v>
+      </c>
+      <c r="G31" t="n">
+        <v>1</v>
+      </c>
+      <c r="H31" t="inlineStr">
         <is>
           <t>(0.026923076923076925, 'negligible')</t>
         </is>
       </c>
-      <c r="H31" t="n">
+      <c r="I31" t="n">
         <v>4.442307692307693</v>
       </c>
-      <c r="I31" t="n">
+      <c r="J31" t="n">
         <v>4.307692307692307</v>
       </c>
-      <c r="J31" t="n">
-        <v>0.5036681523959258</v>
-      </c>
-      <c r="K31" t="inlineStr">
+      <c r="K31" t="n">
+        <v>1</v>
+      </c>
+      <c r="L31" t="n">
+        <v>1</v>
+      </c>
+      <c r="M31" t="inlineStr">
         <is>
           <t>(0.0, 'negligible')</t>
         </is>
       </c>
-      <c r="L31" t="n">
-        <v>4.190476190476191</v>
-      </c>
-      <c r="M31" t="n">
-        <v>4.521739130434782</v>
-      </c>
       <c r="N31" t="n">
-        <v>0.9913344071766134</v>
-      </c>
-      <c r="O31" t="inlineStr">
-        <is>
-          <t>(-0.32401656314699795, 'small')</t>
+        <v>4.377777777777778</v>
+      </c>
+      <c r="O31" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="P31" t="n">
+        <v>0.4541020301234756</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>1</v>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>(-0.10202020202020202, 'negligible')</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Auditorias de Segurança Externas</t>
+          <t>Undergoing External Security Audits</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>efetividade</t>
+          <t>Effectiveness</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>2.674698795180723</v>
+        <v>3.639344262295082</v>
       </c>
       <c r="D32" t="n">
         <v>3.692307692307693</v>
@@ -2236,55 +2509,64 @@
         <v>3.333333333333333</v>
       </c>
       <c r="F32" t="n">
-        <v>0.1583323424548489</v>
-      </c>
-      <c r="G32" t="inlineStr">
+        <v>0.3166646849096978</v>
+      </c>
+      <c r="G32" t="n">
+        <v>1</v>
+      </c>
+      <c r="H32" t="inlineStr">
         <is>
           <t>(0.20512820512820512, 'small')</t>
         </is>
       </c>
-      <c r="H32" t="n">
+      <c r="I32" t="n">
         <v>3.638297872340425</v>
       </c>
-      <c r="I32" t="n">
+      <c r="J32" t="n">
         <v>3.692307692307693</v>
       </c>
-      <c r="J32" t="n">
-        <v>0.6204965728297285</v>
-      </c>
-      <c r="K32" t="inlineStr">
+      <c r="K32" t="n">
+        <v>0.7731996329356443</v>
+      </c>
+      <c r="L32" t="n">
+        <v>1</v>
+      </c>
+      <c r="M32" t="inlineStr">
         <is>
           <t>(-0.05237315875613748, 'negligible')</t>
         </is>
       </c>
-      <c r="L32" t="n">
-        <v>3.444444444444445</v>
-      </c>
-      <c r="M32" t="n">
-        <v>3.720930232558139</v>
-      </c>
       <c r="N32" t="n">
-        <v>0.8373278099739079</v>
-      </c>
-      <c r="O32" t="inlineStr">
-        <is>
-          <t>(-0.15374677002583978, 'small')</t>
+        <v>3.555555555555555</v>
+      </c>
+      <c r="O32" t="n">
+        <v>3.875</v>
+      </c>
+      <c r="P32" t="n">
+        <v>0.4049596966414034</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>1</v>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>(-0.1375, 'negligible')</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Segurança da Cadeia de Suprimentos de Software</t>
+          <t>Software Supply Chain Security</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>efetividade</t>
+          <t>Effectiveness</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>2.867469879518072</v>
+        <v>3.901639344262295</v>
       </c>
       <c r="D33" t="n">
         <v>3.941176470588236</v>
@@ -2293,55 +2575,64 @@
         <v>3.7</v>
       </c>
       <c r="F33" t="n">
-        <v>0.204382689720462</v>
-      </c>
-      <c r="G33" t="inlineStr">
+        <v>0.4087653794409241</v>
+      </c>
+      <c r="G33" t="n">
+        <v>1</v>
+      </c>
+      <c r="H33" t="inlineStr">
         <is>
           <t>(0.1607843137254902, 'small')</t>
         </is>
       </c>
-      <c r="H33" t="n">
+      <c r="I33" t="n">
         <v>3.916666666666667</v>
       </c>
-      <c r="I33" t="n">
+      <c r="J33" t="n">
         <v>3.75</v>
       </c>
-      <c r="J33" t="n">
-        <v>0.5154181669270358</v>
-      </c>
-      <c r="K33" t="inlineStr">
+      <c r="K33" t="n">
+        <v>0.9845789530835082</v>
+      </c>
+      <c r="L33" t="n">
+        <v>1</v>
+      </c>
+      <c r="M33" t="inlineStr">
         <is>
           <t>(-0.005208333333333333, 'negligible')</t>
         </is>
       </c>
-      <c r="L33" t="n">
-        <v>3.882352941176471</v>
-      </c>
-      <c r="M33" t="n">
-        <v>3.909090909090909</v>
-      </c>
       <c r="N33" t="n">
-        <v>0.553589883372229</v>
-      </c>
-      <c r="O33" t="inlineStr">
-        <is>
-          <t>(-0.020053475935828877, 'negligible')</t>
+        <v>3.844444444444445</v>
+      </c>
+      <c r="O33" t="n">
+        <v>4.0625</v>
+      </c>
+      <c r="P33" t="n">
+        <v>0.5422540860939202</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>1</v>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>(-0.1, 'negligible')</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Revisão de Código</t>
+          <t>Code Review</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>frequência</t>
+          <t>Frequency of use</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>2.819277108433735</v>
+        <v>3.12</v>
       </c>
       <c r="D34" t="n">
         <v>3.186440677966102</v>
@@ -2350,55 +2641,64 @@
         <v>2.875</v>
       </c>
       <c r="F34" t="n">
-        <v>0.06994480294336693</v>
-      </c>
-      <c r="G34" t="inlineStr">
+        <v>0.1398896058867339</v>
+      </c>
+      <c r="G34" t="n">
+        <v>1</v>
+      </c>
+      <c r="H34" t="inlineStr">
         <is>
           <t>(0.2277542372881356, 'small')</t>
         </is>
       </c>
-      <c r="H34" t="n">
+      <c r="I34" t="n">
         <v>3.051724137931035</v>
       </c>
-      <c r="I34" t="n">
+      <c r="J34" t="n">
         <v>3.4</v>
       </c>
-      <c r="J34" t="n">
-        <v>0.8998849873759899</v>
-      </c>
-      <c r="K34" t="inlineStr">
+      <c r="K34" t="n">
+        <v>0.2053910779012112</v>
+      </c>
+      <c r="L34" t="n">
+        <v>1</v>
+      </c>
+      <c r="M34" t="inlineStr">
         <is>
           <t>(-0.20114942528735633, 'small')</t>
         </is>
       </c>
-      <c r="L34" t="n">
-        <v>3.125</v>
-      </c>
-      <c r="M34" t="n">
-        <v>3.117647058823529</v>
-      </c>
       <c r="N34" t="n">
-        <v>0.5721063028071289</v>
-      </c>
-      <c r="O34" t="inlineStr">
-        <is>
-          <t>(-0.02369281045751634, 'negligible')</t>
+        <v>3.26</v>
+      </c>
+      <c r="O34" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="P34" t="n">
+        <v>0.04274550310121129</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>0.4274550310121129</v>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>(0.2712, 'small')</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Modelagem de Ameaças</t>
+          <t>Threat Modeling</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>frequência</t>
+          <t>Frequency of use</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>1.855421686746988</v>
+        <v>2.701754385964912</v>
       </c>
       <c r="D35" t="n">
         <v>2.803921568627451</v>
@@ -2407,55 +2707,64 @@
         <v>1.833333333333333</v>
       </c>
       <c r="F35" t="n">
-        <v>0.01595814319922114</v>
-      </c>
-      <c r="G35" t="inlineStr">
+        <v>0.03191628639844227</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0.4787442959766341</v>
+      </c>
+      <c r="H35" t="inlineStr">
         <is>
           <t>(0.5163398692810458, 'large')</t>
         </is>
       </c>
-      <c r="H35" t="n">
+      <c r="I35" t="n">
         <v>2.533333333333333</v>
       </c>
-      <c r="I35" t="n">
+      <c r="J35" t="n">
         <v>3.363636363636364</v>
       </c>
-      <c r="J35" t="n">
-        <v>0.9954329602934833</v>
-      </c>
-      <c r="K35" t="inlineStr">
+      <c r="K35" t="n">
+        <v>0.009727742158777305</v>
+      </c>
+      <c r="L35" t="n">
+        <v>0.1556438745404369</v>
+      </c>
+      <c r="M35" t="inlineStr">
         <is>
           <t>(-0.48484848484848486, 'large')</t>
         </is>
       </c>
-      <c r="L35" t="n">
-        <v>2.9375</v>
-      </c>
-      <c r="M35" t="n">
-        <v>2.609756097560976</v>
-      </c>
       <c r="N35" t="n">
-        <v>0.09409094751979175</v>
-      </c>
-      <c r="O35" t="inlineStr">
-        <is>
-          <t>(0.21646341463414634, 'small')</t>
+        <v>2.934782608695652</v>
+      </c>
+      <c r="O35" t="n">
+        <v>1.727272727272727</v>
+      </c>
+      <c r="P35" t="n">
+        <v>0.0002903447714119532</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>0.004645516342591251</v>
+      </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>(0.6758893280632411, 'large')</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Identificação de Casos de Abuso/Mau Uso</t>
+          <t>Identifying Abuse/Misuse Cases</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>frequência</t>
+          <t>Frequency of use</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>1.855421686746988</v>
+        <v>2.851851851851852</v>
       </c>
       <c r="D36" t="n">
         <v>2.957446808510638</v>
@@ -2464,55 +2773,64 @@
         <v>2.142857142857143</v>
       </c>
       <c r="F36" t="n">
-        <v>0.02453726294407041</v>
-      </c>
-      <c r="G36" t="inlineStr">
+        <v>0.04907452588814082</v>
+      </c>
+      <c r="G36" t="n">
+        <v>0.6868643648903104</v>
+      </c>
+      <c r="H36" t="inlineStr">
         <is>
           <t>(0.44680851063829785, 'medium')</t>
         </is>
       </c>
-      <c r="H36" t="n">
+      <c r="I36" t="n">
         <v>2.857142857142857</v>
       </c>
-      <c r="I36" t="n">
+      <c r="J36" t="n">
         <v>2.818181818181818</v>
       </c>
-      <c r="J36" t="n">
-        <v>0.3915703621429372</v>
-      </c>
-      <c r="K36" t="inlineStr">
+      <c r="K36" t="n">
+        <v>0.7831407242858743</v>
+      </c>
+      <c r="L36" t="n">
+        <v>1</v>
+      </c>
+      <c r="M36" t="inlineStr">
         <is>
           <t>(0.05411255411255411, 'negligible')</t>
         </is>
       </c>
-      <c r="L36" t="n">
-        <v>3.066666666666667</v>
-      </c>
-      <c r="M36" t="n">
-        <v>2.769230769230769</v>
-      </c>
       <c r="N36" t="n">
-        <v>0.2007368542164462</v>
-      </c>
-      <c r="O36" t="inlineStr">
-        <is>
-          <t>(0.14358974358974358, 'negligible')</t>
+        <v>3.046511627906977</v>
+      </c>
+      <c r="O36" t="n">
+        <v>2.090909090909091</v>
+      </c>
+      <c r="P36" t="n">
+        <v>0.004613113673975803</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>0.06458359143566125</v>
+      </c>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>(0.5348837209302325, 'large')</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Análise de Riscos Arquiteturais</t>
+          <t>Architectural Risk Analysis</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>frequência</t>
+          <t>Frequency of use</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>1.939759036144578</v>
+        <v>2.555555555555555</v>
       </c>
       <c r="D37" t="n">
         <v>2.648148148148148</v>
@@ -2521,55 +2839,64 @@
         <v>2</v>
       </c>
       <c r="F37" t="n">
-        <v>0.02565842388250469</v>
-      </c>
-      <c r="G37" t="inlineStr">
+        <v>0.05131684776500939</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0.6868643648903104</v>
+      </c>
+      <c r="H37" t="inlineStr">
         <is>
           <t>(0.39094650205761317, 'medium')</t>
         </is>
       </c>
-      <c r="H37" t="n">
+      <c r="I37" t="n">
         <v>2.591836734693878</v>
       </c>
-      <c r="I37" t="n">
+      <c r="J37" t="n">
         <v>2.384615384615385</v>
       </c>
-      <c r="J37" t="n">
-        <v>0.1657909000719572</v>
-      </c>
-      <c r="K37" t="inlineStr">
+      <c r="K37" t="n">
+        <v>0.3315818001439144</v>
+      </c>
+      <c r="L37" t="n">
+        <v>1</v>
+      </c>
+      <c r="M37" t="inlineStr">
         <is>
           <t>(0.1695447409733124, 'small')</t>
         </is>
       </c>
-      <c r="L37" t="n">
-        <v>2.523809523809524</v>
-      </c>
-      <c r="M37" t="n">
-        <v>2.571428571428572</v>
-      </c>
       <c r="N37" t="n">
-        <v>0.5152639865963633</v>
-      </c>
-      <c r="O37" t="inlineStr">
-        <is>
-          <t>(-0.0045351473922902496, 'negligible')</t>
+        <v>2.708333333333333</v>
+      </c>
+      <c r="O37" t="n">
+        <v>2.066666666666667</v>
+      </c>
+      <c r="P37" t="n">
+        <v>0.01937984060326573</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>0.2325580872391887</v>
+      </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>(0.38472222222222224, 'medium')</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Testes de Penetração</t>
+          <t>Penetration Testing</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>frequência</t>
+          <t>Frequency of use</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>1.72289156626506</v>
+        <v>2.306451612903226</v>
       </c>
       <c r="D38" t="n">
         <v>2.415094339622641</v>
@@ -2578,55 +2905,64 @@
         <v>1.666666666666667</v>
       </c>
       <c r="F38" t="n">
-        <v>0.03193624110961106</v>
-      </c>
-      <c r="G38" t="inlineStr">
+        <v>0.06387248221922212</v>
+      </c>
+      <c r="G38" t="n">
+        <v>0.7025973044114433</v>
+      </c>
+      <c r="H38" t="inlineStr">
         <is>
           <t>(0.37735849056603776, 'medium')</t>
         </is>
       </c>
-      <c r="H38" t="n">
+      <c r="I38" t="n">
         <v>2.304347826086957</v>
       </c>
-      <c r="I38" t="n">
+      <c r="J38" t="n">
         <v>2.285714285714286</v>
       </c>
-      <c r="J38" t="n">
-        <v>0.4531394344187425</v>
-      </c>
-      <c r="K38" t="inlineStr">
+      <c r="K38" t="n">
+        <v>0.906278868837485</v>
+      </c>
+      <c r="L38" t="n">
+        <v>1</v>
+      </c>
+      <c r="M38" t="inlineStr">
         <is>
           <t>(0.021739130434782608, 'negligible')</t>
         </is>
       </c>
-      <c r="L38" t="n">
-        <v>2.380952380952381</v>
-      </c>
-      <c r="M38" t="n">
-        <v>2.268292682926829</v>
-      </c>
       <c r="N38" t="n">
-        <v>0.3528767218534068</v>
-      </c>
-      <c r="O38" t="inlineStr">
-        <is>
-          <t>(0.05807200929152149, 'negligible')</t>
+        <v>2.541666666666667</v>
+      </c>
+      <c r="O38" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="P38" t="n">
+        <v>0.001741075232966598</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>0.02611612849449898</v>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>(0.5357142857142857, 'large')</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Gerenciamento de Riscos</t>
+          <t>Risk Management</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>frequência</t>
+          <t>Frequency of use</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>1.975903614457831</v>
+        <v>2.733333333333333</v>
       </c>
       <c r="D39" t="n">
         <v>2.784313725490196</v>
@@ -2635,55 +2971,64 @@
         <v>2.444444444444445</v>
       </c>
       <c r="F39" t="n">
-        <v>0.162542384450883</v>
-      </c>
-      <c r="G39" t="inlineStr">
+        <v>0.3250847689017661</v>
+      </c>
+      <c r="G39" t="n">
+        <v>1</v>
+      </c>
+      <c r="H39" t="inlineStr">
         <is>
           <t>(0.20043572984749455, 'small')</t>
         </is>
       </c>
-      <c r="H39" t="n">
+      <c r="I39" t="n">
         <v>2.636363636363636</v>
       </c>
-      <c r="I39" t="n">
+      <c r="J39" t="n">
         <v>3</v>
       </c>
-      <c r="J39" t="n">
-        <v>0.8859900468009847</v>
-      </c>
-      <c r="K39" t="inlineStr">
+      <c r="K39" t="n">
+        <v>0.2354283200822972</v>
+      </c>
+      <c r="L39" t="n">
+        <v>1</v>
+      </c>
+      <c r="M39" t="inlineStr">
         <is>
           <t>(-0.20454545454545456, 'small')</t>
         </is>
       </c>
-      <c r="L39" t="n">
-        <v>2.705882352941177</v>
-      </c>
-      <c r="M39" t="n">
-        <v>2.744186046511628</v>
-      </c>
       <c r="N39" t="n">
-        <v>0.5307362726922537</v>
-      </c>
-      <c r="O39" t="inlineStr">
-        <is>
-          <t>(-0.01094391244870041, 'negligible')</t>
+        <v>2.931818181818182</v>
+      </c>
+      <c r="O39" t="n">
+        <v>2.1875</v>
+      </c>
+      <c r="P39" t="n">
+        <v>0.01162010296009987</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>0.1510613384812984</v>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>(0.4119318181818182, 'medium')</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Gerenciamento de Vulnerabilidades</t>
+          <t>Vulnerability Management</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>frequência</t>
+          <t>Frequency of use</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>2.63855421686747</v>
+        <v>3.173913043478261</v>
       </c>
       <c r="D40" t="n">
         <v>3.303571428571428</v>
@@ -2692,55 +3037,64 @@
         <v>2.615384615384615</v>
       </c>
       <c r="F40" t="n">
-        <v>0.002929970720970216</v>
-      </c>
-      <c r="G40" t="inlineStr">
+        <v>0.005859941441940432</v>
+      </c>
+      <c r="G40" t="n">
+        <v>0.09375906307104691</v>
+      </c>
+      <c r="H40" t="inlineStr">
         <is>
           <t>(0.46016483516483514, 'medium')</t>
         </is>
       </c>
-      <c r="H40" t="n">
+      <c r="I40" t="n">
         <v>3.115384615384615</v>
       </c>
-      <c r="I40" t="n">
+      <c r="J40" t="n">
         <v>3.4</v>
       </c>
-      <c r="J40" t="n">
-        <v>0.8652183920720244</v>
-      </c>
-      <c r="K40" t="inlineStr">
+      <c r="K40" t="n">
+        <v>0.2766689831659938</v>
+      </c>
+      <c r="L40" t="n">
+        <v>1</v>
+      </c>
+      <c r="M40" t="inlineStr">
         <is>
           <t>(-0.17307692307692307, 'small')</t>
         </is>
       </c>
-      <c r="L40" t="n">
-        <v>3.315789473684211</v>
-      </c>
-      <c r="M40" t="n">
-        <v>3.12</v>
-      </c>
       <c r="N40" t="n">
-        <v>0.2113783979515971</v>
-      </c>
-      <c r="O40" t="inlineStr">
-        <is>
-          <t>(0.11789473684210526, 'negligible')</t>
+        <v>3.306122448979592</v>
+      </c>
+      <c r="O40" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="P40" t="n">
+        <v>0.03469819044862384</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>0.3816800949348623</v>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>(0.3040816326530612, 'small')</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Testes de Segurança Manuais/Automatizados</t>
+          <t>Manual/Automated Security Testing</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>frequência</t>
+          <t>Frequency of use</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>2.602409638554217</v>
+        <v>3</v>
       </c>
       <c r="D41" t="n">
         <v>3.066666666666667</v>
@@ -2749,55 +3103,64 @@
         <v>2.666666666666667</v>
       </c>
       <c r="F41" t="n">
-        <v>0.1056038459021088</v>
-      </c>
-      <c r="G41" t="inlineStr">
+        <v>0.2112076918042176</v>
+      </c>
+      <c r="G41" t="n">
+        <v>1</v>
+      </c>
+      <c r="H41" t="inlineStr">
         <is>
           <t>(0.21944444444444444, 'small')</t>
         </is>
       </c>
-      <c r="H41" t="n">
+      <c r="I41" t="n">
         <v>2.944444444444445</v>
       </c>
-      <c r="I41" t="n">
+      <c r="J41" t="n">
         <v>3.1875</v>
       </c>
-      <c r="J41" t="n">
-        <v>0.7763735580887685</v>
-      </c>
-      <c r="K41" t="inlineStr">
+      <c r="K41" t="n">
+        <v>0.4561233158973054</v>
+      </c>
+      <c r="L41" t="n">
+        <v>1</v>
+      </c>
+      <c r="M41" t="inlineStr">
         <is>
           <t>(-0.11805555555555555, 'negligible')</t>
         </is>
       </c>
-      <c r="L41" t="n">
-        <v>2.916666666666667</v>
-      </c>
-      <c r="M41" t="n">
-        <v>3.041666666666667</v>
-      </c>
       <c r="N41" t="n">
-        <v>0.6448454249616042</v>
-      </c>
-      <c r="O41" t="inlineStr">
-        <is>
-          <t>(-0.050347222222222224, 'negligible')</t>
+        <v>3.098039215686275</v>
+      </c>
+      <c r="O41" t="n">
+        <v>2.761904761904762</v>
+      </c>
+      <c r="P41" t="n">
+        <v>0.2245732134767909</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>1</v>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>(0.1746031746031746, 'small')</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Execução de Testes Fuzz</t>
+          <t>Performing Fuzz Testing</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>frequência</t>
+          <t>Frequency of use</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>1.44578313253012</v>
+        <v>2.790697674418605</v>
       </c>
       <c r="D42" t="n">
         <v>2.85</v>
@@ -2806,55 +3169,64 @@
         <v>2</v>
       </c>
       <c r="F42" t="n">
-        <v>0.144420139805331</v>
-      </c>
-      <c r="G42" t="inlineStr">
+        <v>0.2888402796106619</v>
+      </c>
+      <c r="G42" t="n">
+        <v>1</v>
+      </c>
+      <c r="H42" t="inlineStr">
         <is>
           <t>(0.35833333333333334, 'medium')</t>
         </is>
       </c>
-      <c r="H42" t="n">
+      <c r="I42" t="n">
         <v>2.787878787878788</v>
       </c>
-      <c r="I42" t="n">
+      <c r="J42" t="n">
         <v>2.777777777777778</v>
       </c>
-      <c r="J42" t="n">
-        <v>0.4935434651170891</v>
-      </c>
-      <c r="K42" t="inlineStr">
+      <c r="K42" t="n">
+        <v>0.9870869302341783</v>
+      </c>
+      <c r="L42" t="n">
+        <v>1</v>
+      </c>
+      <c r="M42" t="inlineStr">
         <is>
           <t>(0.006734006734006734, 'negligible')</t>
         </is>
       </c>
-      <c r="L42" t="n">
-        <v>2.6875</v>
-      </c>
-      <c r="M42" t="n">
-        <v>2.851851851851852</v>
-      </c>
       <c r="N42" t="n">
-        <v>0.6600542816943267</v>
-      </c>
-      <c r="O42" t="inlineStr">
-        <is>
-          <t>(-0.06944444444444445, 'negligible')</t>
+        <v>2.871794871794872</v>
+      </c>
+      <c r="O42" t="n">
+        <v>2</v>
+      </c>
+      <c r="P42" t="n">
+        <v>0.1437822278328442</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>1</v>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>(0.42948717948717946, 'medium')</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Engenharia de Requisitos de Segurança</t>
+          <t>Security Requirements Engineering</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>frequência</t>
+          <t>Frequency of use</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>1.710843373493976</v>
+        <v>2.581818181818182</v>
       </c>
       <c r="D43" t="n">
         <v>2.673469387755102</v>
@@ -2863,55 +3235,64 @@
         <v>1.833333333333333</v>
       </c>
       <c r="F43" t="n">
-        <v>0.02453087017465394</v>
-      </c>
-      <c r="G43" t="inlineStr">
+        <v>0.04906174034930789</v>
+      </c>
+      <c r="G43" t="n">
+        <v>0.6868643648903104</v>
+      </c>
+      <c r="H43" t="inlineStr">
         <is>
           <t>(0.47959183673469385, 'large')</t>
         </is>
       </c>
-      <c r="H43" t="n">
+      <c r="I43" t="n">
         <v>2.560975609756098</v>
       </c>
-      <c r="I43" t="n">
+      <c r="J43" t="n">
         <v>2.666666666666667</v>
       </c>
-      <c r="J43" t="n">
-        <v>0.6381899412928471</v>
-      </c>
-      <c r="K43" t="inlineStr">
+      <c r="K43" t="n">
+        <v>0.7402493116396169</v>
+      </c>
+      <c r="L43" t="n">
+        <v>1</v>
+      </c>
+      <c r="M43" t="inlineStr">
         <is>
           <t>(-0.06300813008130081, 'negligible')</t>
         </is>
       </c>
-      <c r="L43" t="n">
-        <v>2.588235294117647</v>
-      </c>
-      <c r="M43" t="n">
-        <v>2.578947368421053</v>
-      </c>
       <c r="N43" t="n">
-        <v>0.4924337521051868</v>
-      </c>
-      <c r="O43" t="inlineStr">
-        <is>
-          <t>(0.0046439628482972135, 'negligible')</t>
+        <v>2.644444444444444</v>
+      </c>
+      <c r="O43" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="P43" t="n">
+        <v>0.2854837434755202</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>1</v>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>(0.2111111111111111, 'small')</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Codificação Segura</t>
+          <t>Secure Coding</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>frequência</t>
+          <t>Frequency of use</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>2.409638554216868</v>
+        <v>3.278688524590164</v>
       </c>
       <c r="D44" t="n">
         <v>3.24</v>
@@ -2920,55 +3301,64 @@
         <v>3.454545454545455</v>
       </c>
       <c r="F44" t="n">
-        <v>0.7109626446406618</v>
-      </c>
-      <c r="G44" t="inlineStr">
+        <v>0.5925042952114929</v>
+      </c>
+      <c r="G44" t="n">
+        <v>1</v>
+      </c>
+      <c r="H44" t="inlineStr">
         <is>
           <t>(-0.09454545454545454, 'negligible')</t>
         </is>
       </c>
-      <c r="H44" t="n">
+      <c r="I44" t="n">
         <v>3.148936170212766</v>
       </c>
-      <c r="I44" t="n">
+      <c r="J44" t="n">
         <v>3.75</v>
       </c>
-      <c r="J44" t="n">
-        <v>0.9571694596371743</v>
-      </c>
-      <c r="K44" t="inlineStr">
+      <c r="K44" t="n">
+        <v>0.0895729599892756</v>
+      </c>
+      <c r="L44" t="n">
+        <v>1</v>
+      </c>
+      <c r="M44" t="inlineStr">
         <is>
           <t>(-0.2872340425531915, 'small')</t>
         </is>
       </c>
-      <c r="L44" t="n">
-        <v>3.052631578947369</v>
-      </c>
-      <c r="M44" t="n">
-        <v>3.380952380952381</v>
-      </c>
       <c r="N44" t="n">
-        <v>0.9600424168616428</v>
-      </c>
-      <c r="O44" t="inlineStr">
-        <is>
-          <t>(-0.2506265664160401, 'small')</t>
+        <v>3.209302325581395</v>
+      </c>
+      <c r="O44" t="n">
+        <v>3.444444444444445</v>
+      </c>
+      <c r="P44" t="n">
+        <v>0.4006810167010851</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>1</v>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>(-0.12403100775193798, 'negligible')</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Resposta Emergencial ao Código</t>
+          <t>Emergency Codebase Response</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>frequência</t>
+          <t>Frequency of use</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>1.469879518072289</v>
+        <v>2.904761904761905</v>
       </c>
       <c r="D45" t="n">
         <v>2.891891891891892</v>
@@ -2977,55 +3367,64 @@
         <v>3</v>
       </c>
       <c r="F45" t="n">
-        <v>0.6125956653792488</v>
-      </c>
-      <c r="G45" t="inlineStr">
+        <v>0.8062856396772407</v>
+      </c>
+      <c r="G45" t="n">
+        <v>1</v>
+      </c>
+      <c r="H45" t="inlineStr">
         <is>
           <t>(-0.07027027027027027, 'negligible')</t>
         </is>
       </c>
-      <c r="H45" t="n">
+      <c r="I45" t="n">
         <v>2.766666666666667</v>
       </c>
-      <c r="I45" t="n">
+      <c r="J45" t="n">
         <v>3.272727272727273</v>
       </c>
-      <c r="J45" t="n">
-        <v>0.8426130714636795</v>
-      </c>
-      <c r="K45" t="inlineStr">
+      <c r="K45" t="n">
+        <v>0.3298954332663183</v>
+      </c>
+      <c r="L45" t="n">
+        <v>1</v>
+      </c>
+      <c r="M45" t="inlineStr">
         <is>
           <t>(-0.19393939393939394, 'small')</t>
         </is>
       </c>
-      <c r="L45" t="n">
-        <v>2.818181818181818</v>
-      </c>
-      <c r="M45" t="n">
-        <v>2.935483870967742</v>
-      </c>
       <c r="N45" t="n">
-        <v>0.6632854400493733</v>
-      </c>
-      <c r="O45" t="inlineStr">
-        <is>
-          <t>(-0.07917888563049853, 'negligible')</t>
+        <v>3.03125</v>
+      </c>
+      <c r="O45" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="P45" t="n">
+        <v>0.1866000973912028</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>1</v>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>(0.26875, 'small')</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Configurações e Gerenciamento de Segurança</t>
+          <t>Security Configuration and Management</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>frequência</t>
+          <t>Frequency of use</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>2.084337349397591</v>
+        <v>2.932203389830509</v>
       </c>
       <c r="D46" t="n">
         <v>2.959183673469388</v>
@@ -3034,55 +3433,64 @@
         <v>2.8</v>
       </c>
       <c r="F46" t="n">
-        <v>0.2652836868509597</v>
-      </c>
-      <c r="G46" t="inlineStr">
+        <v>0.5305673737019194</v>
+      </c>
+      <c r="G46" t="n">
+        <v>1</v>
+      </c>
+      <c r="H46" t="inlineStr">
         <is>
           <t>(0.12244897959183673, 'negligible')</t>
         </is>
       </c>
-      <c r="H46" t="n">
+      <c r="I46" t="n">
         <v>2.847826086956522</v>
       </c>
-      <c r="I46" t="n">
+      <c r="J46" t="n">
         <v>3.25</v>
       </c>
-      <c r="J46" t="n">
-        <v>0.877564821973723</v>
-      </c>
-      <c r="K46" t="inlineStr">
+      <c r="K46" t="n">
+        <v>0.2531735626515067</v>
+      </c>
+      <c r="L46" t="n">
+        <v>1</v>
+      </c>
+      <c r="M46" t="inlineStr">
         <is>
           <t>(-0.20652173913043478, 'small')</t>
         </is>
       </c>
-      <c r="L46" t="n">
-        <v>2.777777777777778</v>
-      </c>
-      <c r="M46" t="n">
-        <v>3</v>
-      </c>
       <c r="N46" t="n">
-        <v>0.7946954742885463</v>
-      </c>
-      <c r="O46" t="inlineStr">
-        <is>
-          <t>(-0.12737127371273713, 'negligible')</t>
+        <v>3.023809523809524</v>
+      </c>
+      <c r="O46" t="n">
+        <v>2.705882352941177</v>
+      </c>
+      <c r="P46" t="n">
+        <v>0.2242974485921746</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>1</v>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>(0.19467787114845939, 'small')</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Monitoramento de Eventos de Segurança</t>
+          <t>Monitoring for Security Events</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>frequência</t>
+          <t>Frequency of use</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>2.265060240963856</v>
+        <v>3.133333333333333</v>
       </c>
       <c r="D47" t="n">
         <v>3.208333333333333</v>
@@ -3091,55 +3499,64 @@
         <v>2.833333333333333</v>
       </c>
       <c r="F47" t="n">
-        <v>0.103383185140217</v>
-      </c>
-      <c r="G47" t="inlineStr">
+        <v>0.2067663702804341</v>
+      </c>
+      <c r="G47" t="n">
+        <v>1</v>
+      </c>
+      <c r="H47" t="inlineStr">
         <is>
           <t>(0.2222222222222222, 'small')</t>
         </is>
       </c>
-      <c r="H47" t="n">
+      <c r="I47" t="n">
         <v>3.044444444444444</v>
       </c>
-      <c r="I47" t="n">
+      <c r="J47" t="n">
         <v>3.538461538461538</v>
       </c>
-      <c r="J47" t="n">
-        <v>0.9422103608738299</v>
-      </c>
-      <c r="K47" t="inlineStr">
+      <c r="K47" t="n">
+        <v>0.1203207934016647</v>
+      </c>
+      <c r="L47" t="n">
+        <v>1</v>
+      </c>
+      <c r="M47" t="inlineStr">
         <is>
           <t>(-0.26495726495726496, 'small')</t>
         </is>
       </c>
-      <c r="L47" t="n">
-        <v>3.052631578947369</v>
-      </c>
-      <c r="M47" t="n">
-        <v>3.170731707317073</v>
-      </c>
       <c r="N47" t="n">
-        <v>0.7583326063409297</v>
-      </c>
-      <c r="O47" t="inlineStr">
-        <is>
-          <t>(-0.10397946084724005, 'negligible')</t>
+        <v>3.13953488372093</v>
+      </c>
+      <c r="O47" t="n">
+        <v>3.117647058823529</v>
+      </c>
+      <c r="P47" t="n">
+        <v>0.8807536259375922</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>1</v>
+      </c>
+      <c r="R47" t="inlineStr">
+        <is>
+          <t>(0.024623803009575923, 'negligible')</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Auditorias de Segurança Externas</t>
+          <t>Undergoing External Security Audits</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>frequência</t>
+          <t>Frequency of use</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>1.180722891566265</v>
+        <v>1.92156862745098</v>
       </c>
       <c r="D48" t="n">
         <v>1.914893617021277</v>
@@ -3148,55 +3565,64 @@
         <v>2</v>
       </c>
       <c r="F48" t="n">
-        <v>0.5300216790615842</v>
-      </c>
-      <c r="G48" t="inlineStr">
+        <v>0.9699570314876811</v>
+      </c>
+      <c r="G48" t="n">
+        <v>1</v>
+      </c>
+      <c r="H48" t="inlineStr">
         <is>
           <t>(-0.015957446808510637, 'negligible')</t>
         </is>
       </c>
-      <c r="H48" t="n">
+      <c r="I48" t="n">
         <v>1.769230769230769</v>
       </c>
-      <c r="I48" t="n">
+      <c r="J48" t="n">
         <v>2.363636363636364</v>
       </c>
-      <c r="J48" t="n">
-        <v>0.9523271422105293</v>
-      </c>
-      <c r="K48" t="inlineStr">
+      <c r="K48" t="n">
+        <v>0.1004701694963293</v>
+      </c>
+      <c r="L48" t="n">
+        <v>1</v>
+      </c>
+      <c r="M48" t="inlineStr">
         <is>
           <t>(-0.30536130536130535, 'small')</t>
         </is>
       </c>
-      <c r="L48" t="n">
-        <v>1.8125</v>
-      </c>
-      <c r="M48" t="n">
-        <v>1.971428571428572</v>
-      </c>
       <c r="N48" t="n">
-        <v>0.7073105357695193</v>
-      </c>
-      <c r="O48" t="inlineStr">
-        <is>
-          <t>(-0.0875, 'negligible')</t>
+        <v>1.951219512195122</v>
+      </c>
+      <c r="O48" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="P48" t="n">
+        <v>0.6100084673269991</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>1</v>
+      </c>
+      <c r="R48" t="inlineStr">
+        <is>
+          <t>(0.1, 'negligible')</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Segurança da Cadeia de Suprimentos de Software</t>
+          <t>Software Supply Chain Security</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>frequência</t>
+          <t>Frequency of use</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>1.614457831325301</v>
+        <v>2.73469387755102</v>
       </c>
       <c r="D49" t="n">
         <v>2.727272727272727</v>
@@ -3205,51 +3631,60 @@
         <v>2.8</v>
       </c>
       <c r="F49" t="n">
-        <v>0.5274961299591371</v>
-      </c>
-      <c r="G49" t="inlineStr">
+        <v>0.9724875188251048</v>
+      </c>
+      <c r="G49" t="n">
+        <v>1</v>
+      </c>
+      <c r="H49" t="inlineStr">
         <is>
           <t>(-0.013636363636363636, 'negligible')</t>
         </is>
       </c>
-      <c r="H49" t="n">
+      <c r="I49" t="n">
         <v>2.631578947368421</v>
       </c>
-      <c r="I49" t="n">
+      <c r="J49" t="n">
         <v>3.1</v>
       </c>
-      <c r="J49" t="n">
-        <v>0.9238034411364168</v>
-      </c>
-      <c r="K49" t="inlineStr">
+      <c r="K49" t="n">
+        <v>0.160132207155612</v>
+      </c>
+      <c r="L49" t="n">
+        <v>1</v>
+      </c>
+      <c r="M49" t="inlineStr">
         <is>
           <t>(-0.28157894736842104, 'small')</t>
         </is>
       </c>
-      <c r="L49" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="M49" t="n">
-        <v>2.794117647058823</v>
-      </c>
       <c r="N49" t="n">
-        <v>0.7726215816398327</v>
-      </c>
-      <c r="O49" t="inlineStr">
-        <is>
-          <t>(-0.12745098039215685, 'negligible')</t>
+        <v>2.825</v>
+      </c>
+      <c r="O49" t="n">
+        <v>2.333333333333333</v>
+      </c>
+      <c r="P49" t="n">
+        <v>0.182017406688623</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>1</v>
+      </c>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>(0.2777777777777778, 'small')</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Revisão de Código</t>
+          <t>Code Review</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>essencialidade</t>
+          <t>Essentiality</t>
         </is>
       </c>
       <c r="C50" t="n">
@@ -3262,51 +3697,60 @@
         <v>4.142857142857143</v>
       </c>
       <c r="F50" t="n">
-        <v>0.128837353896481</v>
-      </c>
-      <c r="G50" t="inlineStr">
+        <v>0.2576747077929621</v>
+      </c>
+      <c r="G50" t="n">
+        <v>1</v>
+      </c>
+      <c r="H50" t="inlineStr">
         <is>
           <t>(0.14516129032258066, 'negligible')</t>
         </is>
       </c>
-      <c r="H50" t="n">
+      <c r="I50" t="n">
         <v>4.384615384615385</v>
       </c>
-      <c r="I50" t="n">
+      <c r="J50" t="n">
         <v>4.6875</v>
       </c>
-      <c r="J50" t="n">
-        <v>0.908389110141675</v>
-      </c>
-      <c r="K50" t="inlineStr">
+      <c r="K50" t="n">
+        <v>0.1877547863314838</v>
+      </c>
+      <c r="L50" t="n">
+        <v>1</v>
+      </c>
+      <c r="M50" t="inlineStr">
         <is>
           <t>(-0.18653846153846154, 'small')</t>
         </is>
       </c>
-      <c r="L50" t="n">
-        <v>4.346153846153846</v>
-      </c>
-      <c r="M50" t="n">
-        <v>4.491228070175438</v>
-      </c>
       <c r="N50" t="n">
-        <v>0.937605369017222</v>
-      </c>
-      <c r="O50" t="inlineStr">
-        <is>
-          <t>(-0.18286099865047234, 'small')</t>
+        <v>4.473684210526316</v>
+      </c>
+      <c r="O50" t="n">
+        <v>4.384615384615385</v>
+      </c>
+      <c r="P50" t="n">
+        <v>0.387903807849921</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>1</v>
+      </c>
+      <c r="R50" t="inlineStr">
+        <is>
+          <t>(0.1039136302294197, 'negligible')</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Modelagem de Ameaças</t>
+          <t>Threat Modeling</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>essencialidade</t>
+          <t>Essentiality</t>
         </is>
       </c>
       <c r="C51" t="n">
@@ -3319,51 +3763,60 @@
         <v>3.952380952380953</v>
       </c>
       <c r="F51" t="n">
-        <v>0.2261097113360939</v>
-      </c>
-      <c r="G51" t="inlineStr">
+        <v>0.4522194226721877</v>
+      </c>
+      <c r="G51" t="n">
+        <v>1</v>
+      </c>
+      <c r="H51" t="inlineStr">
         <is>
           <t>(0.10215053763440861, 'negligible')</t>
         </is>
       </c>
-      <c r="H51" t="n">
+      <c r="I51" t="n">
         <v>4.123076923076923</v>
       </c>
-      <c r="I51" t="n">
+      <c r="J51" t="n">
         <v>4.5625</v>
       </c>
-      <c r="J51" t="n">
-        <v>0.9597347927988793</v>
-      </c>
-      <c r="K51" t="inlineStr">
+      <c r="K51" t="n">
+        <v>0.08278215109918179</v>
+      </c>
+      <c r="L51" t="n">
+        <v>1</v>
+      </c>
+      <c r="M51" t="inlineStr">
         <is>
           <t>(-0.2605769230769231, 'small')</t>
         </is>
       </c>
-      <c r="L51" t="n">
-        <v>4.192307692307693</v>
-      </c>
-      <c r="M51" t="n">
-        <v>4.245614035087719</v>
-      </c>
       <c r="N51" t="n">
-        <v>0.7757654910794362</v>
-      </c>
-      <c r="O51" t="inlineStr">
-        <is>
-          <t>(-0.0951417004048583, 'negligible')</t>
+        <v>4.263157894736842</v>
+      </c>
+      <c r="O51" t="n">
+        <v>4.153846153846154</v>
+      </c>
+      <c r="P51" t="n">
+        <v>0.7206174753593566</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>1</v>
+      </c>
+      <c r="R51" t="inlineStr">
+        <is>
+          <t>(0.04588394062078273, 'negligible')</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Identificação de Casos de Abuso/Mau Uso</t>
+          <t>Identifying Abuse/Misuse Cases</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>essencialidade</t>
+          <t>Essentiality</t>
         </is>
       </c>
       <c r="C52" t="n">
@@ -3376,51 +3829,60 @@
         <v>4</v>
       </c>
       <c r="F52" t="n">
-        <v>0.6878676187783185</v>
-      </c>
-      <c r="G52" t="inlineStr">
+        <v>0.6321642227211801</v>
+      </c>
+      <c r="G52" t="n">
+        <v>1</v>
+      </c>
+      <c r="H52" t="inlineStr">
         <is>
           <t>(-0.06682027649769585, 'negligible')</t>
         </is>
       </c>
-      <c r="H52" t="n">
+      <c r="I52" t="n">
         <v>4.046153846153846</v>
       </c>
-      <c r="I52" t="n">
+      <c r="J52" t="n">
         <v>3.9375</v>
       </c>
-      <c r="J52" t="n">
-        <v>0.285341217851656</v>
-      </c>
-      <c r="K52" t="inlineStr">
+      <c r="K52" t="n">
+        <v>0.570682435703312</v>
+      </c>
+      <c r="L52" t="n">
+        <v>1</v>
+      </c>
+      <c r="M52" t="inlineStr">
         <is>
           <t>(0.0875, 'negligible')</t>
         </is>
       </c>
-      <c r="L52" t="n">
-        <v>4.153846153846154</v>
-      </c>
-      <c r="M52" t="n">
-        <v>4</v>
-      </c>
       <c r="N52" t="n">
-        <v>0.3064070242872721</v>
-      </c>
-      <c r="O52" t="inlineStr">
-        <is>
-          <t>(0.06612685560053981, 'negligible')</t>
+        <v>4.052631578947368</v>
+      </c>
+      <c r="O52" t="n">
+        <v>4.038461538461538</v>
+      </c>
+      <c r="P52" t="n">
+        <v>0.8962278057264841</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>1</v>
+      </c>
+      <c r="R52" t="inlineStr">
+        <is>
+          <t>(-0.017543859649122806, 'negligible')</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Análise de Riscos Arquiteturais</t>
+          <t>Architectural Risk Analysis</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>essencialidade</t>
+          <t>Essentiality</t>
         </is>
       </c>
       <c r="C53" t="n">
@@ -3433,51 +3895,60 @@
         <v>4.238095238095238</v>
       </c>
       <c r="F53" t="n">
-        <v>0.7568748714575558</v>
-      </c>
-      <c r="G53" t="inlineStr">
+        <v>0.4934255409264302</v>
+      </c>
+      <c r="G53" t="n">
+        <v>1</v>
+      </c>
+      <c r="H53" t="inlineStr">
         <is>
           <t>(-0.09293394777265745, 'negligible')</t>
         </is>
       </c>
-      <c r="H53" t="n">
+      <c r="I53" t="n">
         <v>4.246153846153846</v>
       </c>
-      <c r="I53" t="n">
+      <c r="J53" t="n">
         <v>4.3125</v>
       </c>
-      <c r="J53" t="n">
-        <v>0.63922928975339</v>
-      </c>
-      <c r="K53" t="inlineStr">
+      <c r="K53" t="n">
+        <v>0.7312678503481091</v>
+      </c>
+      <c r="L53" t="n">
+        <v>1</v>
+      </c>
+      <c r="M53" t="inlineStr">
         <is>
           <t>(-0.051923076923076926, 'negligible')</t>
         </is>
       </c>
-      <c r="L53" t="n">
-        <v>4.269230769230769</v>
-      </c>
-      <c r="M53" t="n">
-        <v>4.245614035087719</v>
-      </c>
       <c r="N53" t="n">
-        <v>0.6177469975908975</v>
-      </c>
-      <c r="O53" t="inlineStr">
-        <is>
-          <t>(-0.037112010796221326, 'negligible')</t>
+        <v>4.228070175438597</v>
+      </c>
+      <c r="O53" t="n">
+        <v>4.307692307692307</v>
+      </c>
+      <c r="P53" t="n">
+        <v>0.4801093444159008</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>1</v>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>(-0.08974358974358974, 'negligible')</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Testes de Penetração</t>
+          <t>Penetration Testing</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>essencialidade</t>
+          <t>Essentiality</t>
         </is>
       </c>
       <c r="C54" t="n">
@@ -3490,51 +3961,60 @@
         <v>4.142857142857143</v>
       </c>
       <c r="F54" t="n">
-        <v>0.3537663622762965</v>
-      </c>
-      <c r="G54" t="inlineStr">
+        <v>0.707532724552593</v>
+      </c>
+      <c r="G54" t="n">
+        <v>1</v>
+      </c>
+      <c r="H54" t="inlineStr">
         <is>
           <t>(0.04992319508448541, 'negligible')</t>
         </is>
       </c>
-      <c r="H54" t="n">
+      <c r="I54" t="n">
         <v>4.4</v>
       </c>
-      <c r="I54" t="n">
+      <c r="J54" t="n">
         <v>4.1875</v>
       </c>
-      <c r="J54" t="n">
-        <v>0.1425849370009574</v>
-      </c>
-      <c r="K54" t="inlineStr">
+      <c r="K54" t="n">
+        <v>0.2851698740019147</v>
+      </c>
+      <c r="L54" t="n">
+        <v>1</v>
+      </c>
+      <c r="M54" t="inlineStr">
         <is>
           <t>(0.15576923076923077, 'small')</t>
         </is>
       </c>
-      <c r="L54" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="M54" t="n">
-        <v>4.298245614035087</v>
-      </c>
       <c r="N54" t="n">
-        <v>0.289464830135199</v>
-      </c>
-      <c r="O54" t="inlineStr">
-        <is>
-          <t>(0.06882591093117409, 'negligible')</t>
+        <v>4.421052631578948</v>
+      </c>
+      <c r="O54" t="n">
+        <v>4.230769230769231</v>
+      </c>
+      <c r="P54" t="n">
+        <v>0.5203139618722232</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>1</v>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>(0.0796221322537112, 'negligible')</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Gerenciamento de Riscos</t>
+          <t>Risk Management</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>essencialidade</t>
+          <t>Essentiality</t>
         </is>
       </c>
       <c r="C55" t="n">
@@ -3547,51 +4027,60 @@
         <v>4.571428571428571</v>
       </c>
       <c r="F55" t="n">
-        <v>0.9607141335909734</v>
-      </c>
-      <c r="G55" t="inlineStr">
+        <v>0.08058408002883997</v>
+      </c>
+      <c r="G55" t="n">
+        <v>1</v>
+      </c>
+      <c r="H55" t="inlineStr">
         <is>
           <t>(-0.22964669738863286, 'small')</t>
         </is>
       </c>
-      <c r="H55" t="n">
+      <c r="I55" t="n">
         <v>4.323076923076923</v>
       </c>
-      <c r="I55" t="n">
+      <c r="J55" t="n">
         <v>4.5</v>
       </c>
-      <c r="J55" t="n">
-        <v>0.7519789856787016</v>
-      </c>
-      <c r="K55" t="inlineStr">
+      <c r="K55" t="n">
+        <v>0.5044448664675831</v>
+      </c>
+      <c r="L55" t="n">
+        <v>1</v>
+      </c>
+      <c r="M55" t="inlineStr">
         <is>
           <t>(-0.09807692307692308, 'negligible')</t>
         </is>
       </c>
-      <c r="L55" t="n">
-        <v>4.346153846153846</v>
-      </c>
-      <c r="M55" t="n">
-        <v>4.385964912280702</v>
-      </c>
       <c r="N55" t="n">
-        <v>0.7982447964017445</v>
-      </c>
-      <c r="O55" t="inlineStr">
-        <is>
-          <t>(-0.101889338731444, 'negligible')</t>
+        <v>4.298245614035087</v>
+      </c>
+      <c r="O55" t="n">
+        <v>4.538461538461538</v>
+      </c>
+      <c r="P55" t="n">
+        <v>0.2529823436237666</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>1</v>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>(-0.14102564102564102, 'negligible')</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Gerenciamento de Vulnerabilidades</t>
+          <t>Vulnerability Management</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>essencialidade</t>
+          <t>Essentiality</t>
         </is>
       </c>
       <c r="C56" t="n">
@@ -3604,51 +4093,60 @@
         <v>4.476190476190476</v>
       </c>
       <c r="F56" t="n">
-        <v>0.851791699538244</v>
-      </c>
-      <c r="G56" t="inlineStr">
+        <v>0.3022040784283232</v>
+      </c>
+      <c r="G56" t="n">
+        <v>1</v>
+      </c>
+      <c r="H56" t="inlineStr">
         <is>
           <t>(-0.1282642089093702, 'negligible')</t>
         </is>
       </c>
-      <c r="H56" t="n">
+      <c r="I56" t="n">
         <v>4.476923076923077</v>
       </c>
-      <c r="I56" t="n">
+      <c r="J56" t="n">
         <v>4.5625</v>
       </c>
-      <c r="J56" t="n">
-        <v>0.6029936460426667</v>
-      </c>
-      <c r="K56" t="inlineStr">
+      <c r="K56" t="n">
+        <v>0.8049161345591318</v>
+      </c>
+      <c r="L56" t="n">
+        <v>1</v>
+      </c>
+      <c r="M56" t="inlineStr">
         <is>
           <t>(-0.03461538461538462, 'negligible')</t>
         </is>
       </c>
-      <c r="L56" t="n">
-        <v>4.423076923076923</v>
-      </c>
-      <c r="M56" t="n">
-        <v>4.526315789473684</v>
-      </c>
       <c r="N56" t="n">
-        <v>0.8958604604887915</v>
-      </c>
-      <c r="O56" t="inlineStr">
-        <is>
-          <t>(-0.14507422402159245, 'negligible')</t>
+        <v>4.508771929824562</v>
+      </c>
+      <c r="O56" t="n">
+        <v>4.461538461538462</v>
+      </c>
+      <c r="P56" t="n">
+        <v>0.7977016410665299</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>1</v>
+      </c>
+      <c r="R56" t="inlineStr">
+        <is>
+          <t>(-0.030364372469635626, 'negligible')</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Testes de Segurança Manuais/Automatizados</t>
+          <t>Manual/Automated Security Testing</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>essencialidade</t>
+          <t>Essentiality</t>
         </is>
       </c>
       <c r="C57" t="n">
@@ -3661,51 +4159,60 @@
         <v>4.142857142857143</v>
       </c>
       <c r="F57" t="n">
-        <v>0.6654803494745041</v>
-      </c>
-      <c r="G57" t="inlineStr">
+        <v>0.6775889525085567</v>
+      </c>
+      <c r="G57" t="n">
+        <v>1</v>
+      </c>
+      <c r="H57" t="inlineStr">
         <is>
           <t>(-0.055299539170506916, 'negligible')</t>
         </is>
       </c>
-      <c r="H57" t="n">
+      <c r="I57" t="n">
         <v>4.215384615384616</v>
       </c>
-      <c r="I57" t="n">
+      <c r="J57" t="n">
         <v>4.5625</v>
       </c>
-      <c r="J57" t="n">
-        <v>0.8371314219698275</v>
-      </c>
-      <c r="K57" t="inlineStr">
+      <c r="K57" t="n">
+        <v>0.3322731512779646</v>
+      </c>
+      <c r="L57" t="n">
+        <v>1</v>
+      </c>
+      <c r="M57" t="inlineStr">
         <is>
           <t>(-0.1423076923076923, 'negligible')</t>
         </is>
       </c>
-      <c r="L57" t="n">
-        <v>4.307692307692307</v>
-      </c>
-      <c r="M57" t="n">
-        <v>4.298245614035087</v>
-      </c>
       <c r="N57" t="n">
-        <v>0.6873967381587979</v>
-      </c>
-      <c r="O57" t="inlineStr">
-        <is>
-          <t>(-0.059379217273954114, 'negligible')</t>
+        <v>4.350877192982456</v>
+      </c>
+      <c r="O57" t="n">
+        <v>4.192307692307693</v>
+      </c>
+      <c r="P57" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>1</v>
+      </c>
+      <c r="R57" t="inlineStr">
+        <is>
+          <t>(0.0, 'negligible')</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Execução de Testes Fuzz</t>
+          <t>Performing Fuzz Testing</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>essencialidade</t>
+          <t>Essentiality</t>
         </is>
       </c>
       <c r="C58" t="n">
@@ -3718,51 +4225,60 @@
         <v>3.238095238095238</v>
       </c>
       <c r="F58" t="n">
-        <v>0.3695867991013105</v>
-      </c>
-      <c r="G58" t="inlineStr">
+        <v>0.7391735982026211</v>
+      </c>
+      <c r="G58" t="n">
+        <v>1</v>
+      </c>
+      <c r="H58" t="inlineStr">
         <is>
           <t>(0.047619047619047616, 'negligible')</t>
         </is>
       </c>
-      <c r="H58" t="n">
+      <c r="I58" t="n">
         <v>3.415384615384615</v>
       </c>
-      <c r="I58" t="n">
+      <c r="J58" t="n">
         <v>3.25</v>
       </c>
-      <c r="J58" t="n">
-        <v>0.2582904189593527</v>
-      </c>
-      <c r="K58" t="inlineStr">
+      <c r="K58" t="n">
+        <v>0.5165808379187053</v>
+      </c>
+      <c r="L58" t="n">
+        <v>1</v>
+      </c>
+      <c r="M58" t="inlineStr">
         <is>
           <t>(0.10192307692307692, 'negligible')</t>
         </is>
       </c>
-      <c r="L58" t="n">
-        <v>3.692307692307693</v>
-      </c>
-      <c r="M58" t="n">
-        <v>3.245614035087719</v>
-      </c>
       <c r="N58" t="n">
-        <v>0.07822344636228454</v>
-      </c>
-      <c r="O58" t="inlineStr">
-        <is>
-          <t>(0.18758434547908232, 'small')</t>
+        <v>3.385964912280702</v>
+      </c>
+      <c r="O58" t="n">
+        <v>3.384615384615385</v>
+      </c>
+      <c r="P58" t="n">
+        <v>0.9836733305609052</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>1</v>
+      </c>
+      <c r="R58" t="inlineStr">
+        <is>
+          <t>(-0.0033738191632928477, 'negligible')</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Engenharia de Requisitos de Segurança</t>
+          <t>Security Requirements Engineering</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>essencialidade</t>
+          <t>Essentiality</t>
         </is>
       </c>
       <c r="C59" t="n">
@@ -3775,51 +4291,60 @@
         <v>4</v>
       </c>
       <c r="F59" t="n">
-        <v>0.730282383842335</v>
-      </c>
-      <c r="G59" t="inlineStr">
+        <v>0.5469030498907422</v>
+      </c>
+      <c r="G59" t="n">
+        <v>1</v>
+      </c>
+      <c r="H59" t="inlineStr">
         <is>
           <t>(-0.08294930875576037, 'negligible')</t>
         </is>
       </c>
-      <c r="H59" t="n">
+      <c r="I59" t="n">
         <v>4.092307692307692</v>
       </c>
-      <c r="I59" t="n">
+      <c r="J59" t="n">
         <v>4.1875</v>
       </c>
-      <c r="J59" t="n">
-        <v>0.4670113181967164</v>
-      </c>
-      <c r="K59" t="inlineStr">
+      <c r="K59" t="n">
+        <v>0.9340226363934327</v>
+      </c>
+      <c r="L59" t="n">
+        <v>1</v>
+      </c>
+      <c r="M59" t="inlineStr">
         <is>
           <t>(0.013461538461538462, 'negligible')</t>
         </is>
       </c>
-      <c r="L59" t="n">
-        <v>4.192307692307693</v>
-      </c>
-      <c r="M59" t="n">
-        <v>4.087719298245614</v>
-      </c>
       <c r="N59" t="n">
-        <v>0.5958975271501471</v>
-      </c>
-      <c r="O59" t="inlineStr">
-        <is>
-          <t>(-0.030364372469635626, 'negligible')</t>
+        <v>4.192982456140351</v>
+      </c>
+      <c r="O59" t="n">
+        <v>3.961538461538462</v>
+      </c>
+      <c r="P59" t="n">
+        <v>0.5197083071560094</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>1</v>
+      </c>
+      <c r="R59" t="inlineStr">
+        <is>
+          <t>(0.08299595141700405, 'negligible')</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Codificação Segura</t>
+          <t>Secure Coding</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>essencialidade</t>
+          <t>Essentiality</t>
         </is>
       </c>
       <c r="C60" t="n">
@@ -3832,51 +4357,60 @@
         <v>4.285714285714286</v>
       </c>
       <c r="F60" t="n">
-        <v>0.5631377144413664</v>
-      </c>
-      <c r="G60" t="inlineStr">
+        <v>0.8837516947512509</v>
+      </c>
+      <c r="G60" t="n">
+        <v>1</v>
+      </c>
+      <c r="H60" t="inlineStr">
         <is>
           <t>(-0.018433179723502304, 'negligible')</t>
         </is>
       </c>
-      <c r="H60" t="n">
+      <c r="I60" t="n">
         <v>4.430769230769231</v>
       </c>
-      <c r="I60" t="n">
+      <c r="J60" t="n">
         <v>4.625</v>
       </c>
-      <c r="J60" t="n">
-        <v>0.5745041037720968</v>
-      </c>
-      <c r="K60" t="inlineStr">
+      <c r="K60" t="n">
+        <v>0.8623347607911088</v>
+      </c>
+      <c r="L60" t="n">
+        <v>1</v>
+      </c>
+      <c r="M60" t="inlineStr">
         <is>
           <t>(-0.02403846153846154, 'negligible')</t>
         </is>
       </c>
-      <c r="L60" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="M60" t="n">
-        <v>4.456140350877193</v>
-      </c>
       <c r="N60" t="n">
-        <v>0.9174858844691021</v>
-      </c>
-      <c r="O60" t="inlineStr">
-        <is>
-          <t>(-0.15654520917678813, 'small')</t>
+        <v>4.526315789473684</v>
+      </c>
+      <c r="O60" t="n">
+        <v>4.346153846153846</v>
+      </c>
+      <c r="P60" t="n">
+        <v>0.6209071464203055</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>1</v>
+      </c>
+      <c r="R60" t="inlineStr">
+        <is>
+          <t>(0.05668016194331984, 'negligible')</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Resposta Emergencial ao Código</t>
+          <t>Emergency Codebase Response</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>essencialidade</t>
+          <t>Essentiality</t>
         </is>
       </c>
       <c r="C61" t="n">
@@ -3889,51 +4423,60 @@
         <v>3.714285714285714</v>
       </c>
       <c r="F61" t="n">
-        <v>0.5502162531517411</v>
-      </c>
-      <c r="G61" t="inlineStr">
+        <v>0.9082603288825858</v>
+      </c>
+      <c r="G61" t="n">
+        <v>1</v>
+      </c>
+      <c r="H61" t="inlineStr">
         <is>
           <t>(-0.016897081413210446, 'negligible')</t>
         </is>
       </c>
-      <c r="H61" t="n">
+      <c r="I61" t="n">
         <v>3.861538461538462</v>
       </c>
-      <c r="I61" t="n">
+      <c r="J61" t="n">
         <v>3.75</v>
       </c>
-      <c r="J61" t="n">
-        <v>0.187143127081898</v>
-      </c>
-      <c r="K61" t="inlineStr">
+      <c r="K61" t="n">
+        <v>0.3742862541637959</v>
+      </c>
+      <c r="L61" t="n">
+        <v>1</v>
+      </c>
+      <c r="M61" t="inlineStr">
         <is>
           <t>(0.13846153846153847, 'negligible')</t>
         </is>
       </c>
-      <c r="L61" t="n">
-        <v>3.961538461538462</v>
-      </c>
-      <c r="M61" t="n">
-        <v>3.789473684210526</v>
-      </c>
       <c r="N61" t="n">
-        <v>0.4672071170463282</v>
-      </c>
-      <c r="O61" t="inlineStr">
-        <is>
-          <t>(0.011470985155195682, 'negligible')</t>
+        <v>3.824561403508772</v>
+      </c>
+      <c r="O61" t="n">
+        <v>3.884615384615385</v>
+      </c>
+      <c r="P61" t="n">
+        <v>0.8611807988638691</v>
+      </c>
+      <c r="Q61" t="n">
+        <v>1</v>
+      </c>
+      <c r="R61" t="inlineStr">
+        <is>
+          <t>(-0.023616734143049933, 'negligible')</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Configurações e Gerenciamento de Segurança</t>
+          <t>Security Configuration and Management</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>essencialidade</t>
+          <t>Essentiality</t>
         </is>
       </c>
       <c r="C62" t="n">
@@ -3946,51 +4489,60 @@
         <v>4.285714285714286</v>
       </c>
       <c r="F62" t="n">
-        <v>0.8154264066615253</v>
-      </c>
-      <c r="G62" t="inlineStr">
+        <v>0.3753568072925636</v>
+      </c>
+      <c r="G62" t="n">
+        <v>1</v>
+      </c>
+      <c r="H62" t="inlineStr">
         <is>
           <t>(-0.11827956989247312, 'negligible')</t>
         </is>
       </c>
-      <c r="H62" t="n">
+      <c r="I62" t="n">
         <v>4.261538461538461</v>
       </c>
-      <c r="I62" t="n">
+      <c r="J62" t="n">
         <v>4.3125</v>
       </c>
-      <c r="J62" t="n">
-        <v>0.5521983478094028</v>
-      </c>
-      <c r="K62" t="inlineStr">
+      <c r="K62" t="n">
+        <v>0.9059918375275888</v>
+      </c>
+      <c r="L62" t="n">
+        <v>1</v>
+      </c>
+      <c r="M62" t="inlineStr">
         <is>
           <t>(-0.01826923076923077, 'negligible')</t>
         </is>
       </c>
-      <c r="L62" t="n">
-        <v>4.269230769230769</v>
-      </c>
-      <c r="M62" t="n">
-        <v>4.280701754385965</v>
-      </c>
       <c r="N62" t="n">
-        <v>0.7302853369684611</v>
-      </c>
-      <c r="O62" t="inlineStr">
-        <is>
-          <t>(-0.07557354925775979, 'negligible')</t>
+        <v>4.263157894736842</v>
+      </c>
+      <c r="O62" t="n">
+        <v>4.307692307692307</v>
+      </c>
+      <c r="P62" t="n">
+        <v>0.7734765467851794</v>
+      </c>
+      <c r="Q62" t="n">
+        <v>1</v>
+      </c>
+      <c r="R62" t="inlineStr">
+        <is>
+          <t>(-0.03643724696356275, 'negligible')</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Monitoramento de Eventos de Segurança</t>
+          <t>Monitoring for Security Events</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>essencialidade</t>
+          <t>Essentiality</t>
         </is>
       </c>
       <c r="C63" t="n">
@@ -4003,51 +4555,60 @@
         <v>4.571428571428571</v>
       </c>
       <c r="F63" t="n">
-        <v>0.956274468906322</v>
-      </c>
-      <c r="G63" t="inlineStr">
+        <v>0.08968752049836509</v>
+      </c>
+      <c r="G63" t="n">
+        <v>1</v>
+      </c>
+      <c r="H63" t="inlineStr">
         <is>
           <t>(-0.21889400921658986, 'small')</t>
         </is>
       </c>
-      <c r="H63" t="n">
+      <c r="I63" t="n">
         <v>4.415384615384616</v>
       </c>
-      <c r="I63" t="n">
+      <c r="J63" t="n">
         <v>4.375</v>
       </c>
-      <c r="J63" t="n">
-        <v>0.4011094394336732</v>
-      </c>
-      <c r="K63" t="inlineStr">
+      <c r="K63" t="n">
+        <v>0.8022188788673463</v>
+      </c>
+      <c r="L63" t="n">
+        <v>1</v>
+      </c>
+      <c r="M63" t="inlineStr">
         <is>
           <t>(0.03653846153846154, 'negligible')</t>
         </is>
       </c>
-      <c r="L63" t="n">
-        <v>4.384615384615385</v>
-      </c>
-      <c r="M63" t="n">
-        <v>4.421052631578948</v>
-      </c>
       <c r="N63" t="n">
-        <v>0.7916413262262267</v>
-      </c>
-      <c r="O63" t="inlineStr">
-        <is>
-          <t>(-0.09716599190283401, 'negligible')</t>
+        <v>4.315789473684211</v>
+      </c>
+      <c r="O63" t="n">
+        <v>4.615384615384615</v>
+      </c>
+      <c r="P63" t="n">
+        <v>0.1806965634531579</v>
+      </c>
+      <c r="Q63" t="n">
+        <v>1</v>
+      </c>
+      <c r="R63" t="inlineStr">
+        <is>
+          <t>(-0.16194331983805668, 'small')</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Auditorias de Segurança Externas</t>
+          <t>Undergoing External Security Audits</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>essencialidade</t>
+          <t>Essentiality</t>
         </is>
       </c>
       <c r="C64" t="n">
@@ -4060,51 +4621,60 @@
         <v>3.619047619047619</v>
       </c>
       <c r="F64" t="n">
-        <v>0.3946861162791896</v>
-      </c>
-      <c r="G64" t="inlineStr">
+        <v>0.7893722325583792</v>
+      </c>
+      <c r="G64" t="n">
+        <v>1</v>
+      </c>
+      <c r="H64" t="inlineStr">
         <is>
           <t>(0.03840245775729647, 'negligible')</t>
         </is>
       </c>
-      <c r="H64" t="n">
+      <c r="I64" t="n">
         <v>3.707692307692308</v>
       </c>
-      <c r="I64" t="n">
+      <c r="J64" t="n">
         <v>3.9375</v>
       </c>
-      <c r="J64" t="n">
-        <v>0.7149149765322487</v>
-      </c>
-      <c r="K64" t="inlineStr">
+      <c r="K64" t="n">
+        <v>0.5785817192153027</v>
+      </c>
+      <c r="L64" t="n">
+        <v>1</v>
+      </c>
+      <c r="M64" t="inlineStr">
         <is>
           <t>(-0.0875, 'negligible')</t>
         </is>
       </c>
-      <c r="L64" t="n">
-        <v>3.807692307692307</v>
-      </c>
-      <c r="M64" t="n">
-        <v>3.736842105263158</v>
-      </c>
       <c r="N64" t="n">
-        <v>0.4230209027059261</v>
-      </c>
-      <c r="O64" t="inlineStr">
-        <is>
-          <t>(0.02631578947368421, 'negligible')</t>
+        <v>3.719298245614035</v>
+      </c>
+      <c r="O64" t="n">
+        <v>3.846153846153846</v>
+      </c>
+      <c r="P64" t="n">
+        <v>0.5296753799566254</v>
+      </c>
+      <c r="Q64" t="n">
+        <v>1</v>
+      </c>
+      <c r="R64" t="inlineStr">
+        <is>
+          <t>(-0.08367071524966262, 'negligible')</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Segurança da Cadeia de Suprimentos de Software</t>
+          <t>Software Supply Chain Security</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>essencialidade</t>
+          <t>Essentiality</t>
         </is>
       </c>
       <c r="C65" t="n">
@@ -4117,39 +4687,48 @@
         <v>3.761904761904762</v>
       </c>
       <c r="F65" t="n">
-        <v>0.2330637014880765</v>
-      </c>
-      <c r="G65" t="inlineStr">
+        <v>0.4661274029761531</v>
+      </c>
+      <c r="G65" t="n">
+        <v>1</v>
+      </c>
+      <c r="H65" t="inlineStr">
         <is>
           <t>(0.09984639016897082, 'negligible')</t>
         </is>
       </c>
-      <c r="H65" t="n">
+      <c r="I65" t="n">
         <v>4.061538461538461</v>
       </c>
-      <c r="I65" t="n">
+      <c r="J65" t="n">
         <v>4.1875</v>
       </c>
-      <c r="J65" t="n">
-        <v>0.6797493540191974</v>
-      </c>
-      <c r="K65" t="inlineStr">
+      <c r="K65" t="n">
+        <v>0.6496823228437956</v>
+      </c>
+      <c r="L65" t="n">
+        <v>1</v>
+      </c>
+      <c r="M65" t="inlineStr">
         <is>
           <t>(-0.06923076923076923, 'negligible')</t>
         </is>
       </c>
-      <c r="L65" t="n">
-        <v>4.346153846153846</v>
-      </c>
-      <c r="M65" t="n">
-        <v>4</v>
-      </c>
       <c r="N65" t="n">
-        <v>0.1066737669381883</v>
-      </c>
-      <c r="O65" t="inlineStr">
-        <is>
-          <t>(0.1592442645074224, 'small')</t>
+        <v>4.245614035087719</v>
+      </c>
+      <c r="O65" t="n">
+        <v>3.807692307692307</v>
+      </c>
+      <c r="P65" t="n">
+        <v>0.1259267920005523</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>1</v>
+      </c>
+      <c r="R65" t="inlineStr">
+        <is>
+          <t>(0.19568151147098514, 'small')</t>
         </is>
       </c>
     </row>
